--- a/extraction/datalink.xlsx
+++ b/extraction/datalink.xlsx
@@ -13,9 +13,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deal facts" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$68</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Deal ledger'!$A$1:$V$72</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rounds'!$A$1:$J$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Questions'!$A$1:$G$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Deal facts'!$A$1:$B$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,31 +439,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V68"/>
+  <dimension ref="A1:V72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="8" customWidth="1" min="6" max="6"/>
     <col width="7" customWidth="1" min="7" max="7"/>
     <col width="9" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
     <col width="7" customWidth="1" min="13" max="13"/>
-    <col width="20" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
     <col width="8" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
-    <col width="60" customWidth="1" min="17" max="17"/>
-    <col width="12" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
     <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="11" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -636,12 +636,12 @@
       <c r="O2" s="2" t="n"/>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>Conditions: none reported. First contact: Party A made an unsolicited request in January 2016 for an in-person meeting, where its President handed Lidsky an unsolicited letter at $10.00 cash per share. Ref: $6.40 close 01/19/2016.</t>
+          <t>First contact: Party A's unsolicited January 2016 request for a meeting; at the 01/19 meeting its President handed over an unsolicited letter proposing $10.00 cash per share. No conditions reported, so Conditions Unclear. Ref: $6.40 close 01/19/2016.</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>received an unsolicited letter from Party A proposing to acquire the Company at a price of $10.00 in cash per share (p. 27)</t>
+          <t>“received an unsolicited letter from Party A proposing to acquire the Company at a price of $10.00 in cash per share” (p. 27)</t>
         </is>
       </c>
       <c r="R2" s="2" t="n"/>
@@ -682,8 +682,8 @@
       <c r="G3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="n"/>
       <c r="K3" s="2" t="n"/>
       <c r="L3" s="2" t="n"/>
@@ -692,12 +692,12 @@
       <c r="O3" s="2" t="n"/>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>Price signal: at the direction of directors Ousley, Blackey and Meland, Lidsky told Party A the board would need to discuss the proposal and that $10.00 was at the very low end of the range the board would consider.</t>
+          <t>Price signal to Party A: at the direction of the chair and two other directors, the CEO said the board would need to discuss the proposal and that $10.00 was at the very low end of the range the board would consider.</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>the proposed price of $10.00 in cash per share was at the very low end of the range Mr. Lidsky expected our board would consider (p. 27)</t>
+          <t>“the proposed price of $10.00 in cash per share was at the very low end of the range Mr. Lidsky expected our board would consider” (p. 27)</t>
         </is>
       </c>
       <c r="R3" s="2" t="n"/>
@@ -736,10 +736,10 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="n"/>
@@ -748,12 +748,12 @@
       <c r="O4" s="2" t="n"/>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>Target's legal counsel (FaegreBD); earliest shown acting: fiduciary-duty presentation to the board on 01/29/2016. Acted throughout, including merger-agreement negotiations.</t>
+          <t>Datalink's (target's) legal counsel; first shown acting at the 01/29/2016 board meeting, advising on fiduciary duties in a potential sale. Counsel throughout, including merger-agreement negotiation with Insight's counsel.</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>Our legal counsel, Faegre Baker Daniels LLP ("FaegreBD"), provided a presentation to our board regarding their fiduciary duties (p. 27)</t>
+          <t>“Our legal counsel, Faegre Baker Daniels LLP ("FaegreBD"), provided a presentation to our board regarding their fiduciary duties” (p. 27)</t>
         </is>
       </c>
       <c r="R4" s="2" t="n"/>
@@ -792,10 +792,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n"/>
+      <c r="I5" s="2" t="n"/>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
       <c r="L5" s="2" t="n"/>
@@ -804,12 +804,12 @@
       <c r="O5" s="2" t="n"/>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>Board decides management should continue to pursue Party A's proposal, mindful of the risk of a leak of a sale process; directs management to approach Raymond James about serving as financial adviser.</t>
+          <t>Board decided management should continue to pursue the Party A opportunity, mindful of concern about a leak of a sale process, and directed management to approach Raymond James as financial adviser. Qualified: a bilateral pursuit of Party A only, no broader sale process.</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
-          <t>determined that our management should continue to pursue the opportunity with Party A while being mindful of our board's concerns regarding a potential leak of a Company sale process (p. 27)</t>
+          <t>“determined that our management should continue to pursue the opportunity with Party A while being mindful of our board's concerns regarding a potential leak” (p. 27)</t>
         </is>
       </c>
       <c r="R5" s="2" t="n"/>
@@ -830,62 +830,54 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>01/29/2016</t>
+          <t>02/04/2016</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
+          <t>Raymond James &amp; Associates, Inc.</t>
         </is>
       </c>
       <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O6" s="2" t="n"/>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>Inferred round: bilateral stage with Party A begins with the board's decision to pursue its approach; executed by the Raymond James contact (02/01), NDA (02/04), data room (02/24) and the mid-March request for a written proposal. No due date. See Q1.</t>
+          <t>Datalink board's financial adviser: contacted 02/01/2016, engagement letter executed 02/04/2016 after board approval (retention date confirmed p. 41). Ran the outreach and bidder communications; delivered the 11/06/2016 fairness opinion.</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>our management should continue to pursue the opportunity with Party A (p. 27)</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“after our board approved the engagement letter, it was executed on February 4, 2016” (p. 27)</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="n"/>
       <c r="S6" s="2" t="n"/>
       <c r="T6" s="4" t="n">
-        <v>42398</v>
+        <v>42404</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>42398</v>
+        <v>42404</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>42398</v>
+        <v>42404</v>
       </c>
     </row>
     <row r="7">
@@ -899,37 +891,43 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Raymond James &amp; Associates, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F7" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="3" t="n"/>
-      <c r="I7" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="2" t="n"/>
+      <c r="I7" s="2" t="n"/>
       <c r="J7" s="2" t="n"/>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="n"/>
-      <c r="M7" s="2" t="n"/>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N7" s="2" t="n"/>
       <c r="O7" s="2" t="n"/>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>Target board's financial adviser. Management contacted Raymond James on 02/01/2016; engagement letter executed 02/04/2016. Delivered fairness opinion 11/06/2016; fee about $3.86 million, mostly contingent on closing (p.48).</t>
+          <t>NDA executed with Party A (entered at #1). Party A, the only bidder then in the process, received limited financial information in a data room opened 02/24/2016.</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>after our board approved the engagement letter, it was executed on February 4, 2016 (p. 27)</t>
+          <t>“We also negotiated and entered into a non-disclosure agreement with Party A on February 4, 2016” (p. 27)</t>
         </is>
       </c>
       <c r="R7" s="2" t="n"/>
@@ -950,48 +948,42 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>02/04/2016</t>
+          <t>mid-March 2016</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="n"/>
-      <c r="I8" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n"/>
+      <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
       <c r="O8" s="2" t="n"/>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>NDA executed with Party A; it was then given limited financial information in a data room opened 02/24/2016, the only party reported in the process at that time.</t>
+          <t>Target requested a written proposal from Party A; the request is dated only 'mid-March'. Party A answered on 03/29 (#8).</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>We also negotiated and entered into a non-disclosure agreement with Party A on February 4, 2016 (p. 27)</t>
+          <t>“As we requested in mid-March 2016, on March 29, 2016, Party A provided a written proposal” (p. 27)</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
@@ -1001,13 +993,13 @@
       </c>
       <c r="S8" s="2" t="n"/>
       <c r="T8" s="4" t="n">
-        <v>42404</v>
+        <v>42444</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>42404</v>
+        <v>42440</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>42404</v>
+        <v>42448</v>
       </c>
     </row>
     <row r="9">
@@ -1016,42 +1008,64 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>mid-March 2016</t>
+          <t>03/29/2016</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n"/>
+          <t>Party A</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F9" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="3" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="2" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N9" s="2" t="n"/>
       <c r="O9" s="2" t="n"/>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>Target requests a written acquisition proposal from Party A; no due date stated.</t>
+          <t>Heavy: contingent on Party A's receipt of financing. Written proposal of at least $10.30 per share, possibly up to $10.75 if certain financial criteria were met (low = stated floor, high = contingent ceiling). Ref: $8.51 close 03/29/2016.</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>As we requested in mid-March 2016, on March 29, 2016, Party A provided a written proposal (p. 27)</t>
+          <t>“Party A provided a written proposal to acquire the Company for a price of at least $10.30 per share, with the offer price potentially being as high as $10.75” (p. 27)</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -1061,13 +1075,13 @@
       </c>
       <c r="S9" s="2" t="n"/>
       <c r="T9" s="4" t="n">
-        <v>42444</v>
+        <v>42458</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>42440</v>
+        <v>42458</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>42448</v>
+        <v>42458</v>
       </c>
     </row>
     <row r="10">
@@ -1076,7 +1090,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>03/29/2016</t>
+          <t>04/12/2016</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1098,7 +1112,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>10.3</v>
@@ -1128,28 +1142,28 @@
       <c r="O10" s="2" t="n"/>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Heavy: offer contingent on Party A obtaining financing. Written proposal at 'at least' $10.30 (Price low), potentially up to $10.75 (Price high) if certain financial criteria were met. Ref: $8.51 close 03/29/2016.</t>
+          <t>Heavy: financing contingency not reported lifted; on 04/20 the board still cited only limited financing information. Updated indication affirming substantially all terms of #8, including price (carried from #8); unspecified changes. Ref: $9.13 close 04/12/2016.</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>a written proposal to acquire the Company for a price of at least $10.30 per share, with the offer price potentially being as high as $10.75 per share (p. 27)</t>
+          <t>“Party A affirmed substantially all of these transaction terms, including the price per share, in an updated indication of interest received on April 12, 2016” (p. 27)</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q1; Q2</t>
         </is>
       </c>
       <c r="S10" s="2" t="n"/>
       <c r="T10" s="4" t="n">
-        <v>42458</v>
+        <v>42472</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>42458</v>
+        <v>42472</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>42458</v>
+        <v>42472</v>
       </c>
     </row>
     <row r="11">
@@ -1158,80 +1172,58 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>04/12/2016</t>
+          <t>04/20/2016</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Party A</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="n"/>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
       <c r="O11" s="2" t="n"/>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Heavy: affirms the terms of #9, including its financing contingency. Updated indication of interest affirming 'substantially all' terms, including the price per share; changes, if any, not described (Q2). Ref: $9.13 close 04/12/2016.</t>
+          <t>Rejected Party A's proposal for now: board had Raymond James tell Party A it was not interested 'at that time' but would consider a definitive proposal with executed financing commitment letters and a higher price. Not an exit: conversations with Party A continued through May. Ref: $8.84 close.</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>Party A affirmed substantially all of these transaction terms, including the price per share, in an updated indication of interest received on April 12, 2016. (p. 27)</t>
+          <t>“our board would consider a definitive proposal offered by Party A that had a higher likelihood of consummation, based on, among other things, executed commitment letters” (p. 28)</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S11" s="2" t="n"/>
       <c r="T11" s="4" t="n">
-        <v>42472</v>
+        <v>42480</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>42472</v>
+        <v>42480</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>42472</v>
+        <v>42480</v>
       </c>
     </row>
     <row r="12">
@@ -1240,7 +1232,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>04/20/2016</t>
+          <t>05/25/2016</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1251,17 +1243,17 @@
       <c r="D12" s="2" t="n"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Target sale decision</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="3" t="n"/>
-      <c r="I12" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
@@ -1270,12 +1262,12 @@
       <c r="O12" s="2" t="n"/>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Price and financing requirement: board will not pursue Party A 'at that time' but would consider a definitive proposal with executed financing commitment letters and a higher price. Not an exit: talks with Party A continued into May and it was on the June outreach list.</t>
+          <t>After a Raymond James review of alternatives (stay independent, consolidation, sale) with buyer and sponsor profiles, board directed the CEO to have Raymond James prepare for a sale process, subject to confirmation on 06/01; instruction given 05/26. Ref: $8.11 close.</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>our board was not interested in pursuing a transaction with Party A at that time, but that our board would consider a definitive proposal offered by Party A (p. 28)</t>
+          <t>“our board directed Mr. Lidsky to instruct Raymond James to prepare for a sale process, subject to confirmation at a board meeting on June 1, 2016” (p. 28)</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
@@ -1285,13 +1277,13 @@
       </c>
       <c r="S12" s="2" t="n"/>
       <c r="T12" s="4" t="n">
-        <v>42480</v>
+        <v>42515</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>42480</v>
+        <v>42515</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>42480</v>
+        <v>42515</v>
       </c>
     </row>
     <row r="13">
@@ -1300,7 +1292,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>05/25/2016</t>
+          <t>06/01/2016</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1318,10 +1310,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="3" t="n"/>
-      <c r="I13" s="3" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
@@ -1330,24 +1322,28 @@
       <c r="O13" s="2" t="n"/>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Board directs Lidsky to have Raymond James prepare for a sale process, subject to confirmation at the 06/01 board meeting (instruction given 05/26). Raymond James presented alternatives, including profiles of strategic buyers and sponsors.</t>
+          <t>Confirmation: board authorized Raymond James to list potential acquirers, including Party A, review the list with management, and begin discussions to gauge interest; discussed timeline and controls on information leakage. Ref: $8.17 close.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>our board directed Mr. Lidsky to instruct Raymond James to prepare for a sale process, subject to confirmation at a board meeting on June 1, 2016 (p. 28)</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="n"/>
+          <t>“our board authorized Raymond James to identify a list of potential acquirers, including Party A, based on our board's input” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="n"/>
       <c r="T13" s="4" t="n">
-        <v>42515</v>
+        <v>42522</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>42515</v>
+        <v>42522</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>42515</v>
+        <v>42522</v>
       </c>
     </row>
     <row r="14">
@@ -1356,7 +1352,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>06/01/2016</t>
+          <t>06/06/2016</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1367,7 +1363,7 @@
       <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Target sale decision</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1376,8 +1372,8 @@
       <c r="G14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="H14" s="3" t="n"/>
-      <c r="I14" s="3" t="n"/>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="n"/>
@@ -1386,24 +1382,28 @@
       <c r="O14" s="2" t="n"/>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Board confirms: authorizes Raymond James to draw up a list of potential acquirers including Party A, review it with management, and begin discussions; timeline and leak control discussed.</t>
+          <t>Round 1 (first outreach wave): Raymond James began contacting strategic acquirers; financial sponsors followed later in June. Party A (live since #1) was included. NDA signers got a management presentation and data-room access for limited diligence.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>our board authorized Raymond James to identify a list of potential acquirers, including Party A, based on our board's input (p. 28)</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="n"/>
+          <t>“On June 6, 2016, Raymond James began contacting potential strategic acquirers, with management's authorization, to gauge their interest in a potential transaction” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S14" s="2" t="n"/>
       <c r="T14" s="4" t="n">
-        <v>42522</v>
+        <v>42527</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>42522</v>
+        <v>42527</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>42522</v>
+        <v>42527</v>
       </c>
     </row>
     <row r="15">
@@ -1412,49 +1412,51 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>06/06/2016</t>
+          <t>from 06/06/2016</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n"/>
+          <t>Insight Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" s="3" t="n"/>
-      <c r="I15" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="n"/>
       <c r="J15" s="2" t="n"/>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="n"/>
-      <c r="M15" s="2" t="n"/>
+      <c r="M15" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="n"/>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Raymond James starts outreach to strategic acquirers (13, including Party A, Party B and Insight); 14 financial sponsors contacted later in June. NDA signers received a management presentation and data-room access for limited diligence. IOI due dates set in #19.</t>
+          <t>Target-initiated contact by Raymond James in the strategic outreach; exact date not stated (on or after 06/06/2016). Insight is a Fortune 500 IT provider (p. 1).</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>On June 6, 2016, Raymond James began contacting potential strategic acquirers, with management's authorization, to gauge their interest in a potential transaction. (p. 28)</t>
-        </is>
-      </c>
-      <c r="R15" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Beginning June 6, Raymond James contacted 13 strategic acquirers (including Party A, Party B and Insight)” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R15" s="2" t="n"/>
       <c r="S15" s="2" t="n"/>
       <c r="T15" s="4" t="n">
         <v>42527</v>
@@ -1462,9 +1464,7 @@
       <c r="U15" s="4" t="n">
         <v>42527</v>
       </c>
-      <c r="V15" s="4" t="n">
-        <v>42527</v>
-      </c>
+      <c r="V15" s="2" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1472,12 +1472,12 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>beginning 06/06/2016</t>
+          <t>from 06/06/2016</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>12 strategic acquirers contacted (incl. Insight, Party B)</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1494,26 +1494,26 @@
         <v>1</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H16" s="3" t="n"/>
-      <c r="I16" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="n"/>
       <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="n"/>
       <c r="M16" s="2" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N16" s="2" t="n"/>
       <c r="O16" s="2" t="n"/>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated. Filing's total of 13 strategic acquirers contacted less Party A, whose first contact is #1. 3 of the 13 did not sign an NDA. Individual contact dates not given.</t>
+          <t>Target-initiated contact by Raymond James in the strategic outreach; exact date not stated (on or after 06/06/2016). Party B is a strategic acquirer (p. 30).</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>Beginning June 6, Raymond James contacted 13 strategic acquirers (including Party A, Party B and Insight), 10 of which (including Party A, Party B and Insight) signed a non-disclosure agreement (p. 28)</t>
+          <t>“Beginning June 6, Raymond James contacted 13 strategic acquirers (including Party A, Party B and Insight)” (p. 28)</t>
         </is>
       </c>
       <c r="R16" s="2" t="n"/>
@@ -1524,7 +1524,7 @@
       <c r="U16" s="4" t="n">
         <v>42527</v>
       </c>
-      <c r="V16" s="4" t="n"/>
+      <c r="V16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>9 strategic NDA signers (incl. Insight, Party B)</t>
+          <t>10 other strategic acquirers contacted</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1547,40 +1547,36 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>NDA signed</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="n"/>
       <c r="J17" s="2" t="n"/>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="n"/>
       <c r="M17" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N17" s="2" t="n"/>
       <c r="O17" s="2" t="n"/>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>Filing's 10 strategic NDA signers less Party A, whose 02/04 NDA is #7; not stated whether Party A signed a new NDA (Q3). All NDAs carried standstills ending on announcement. Execution dates not given.</t>
+          <t>Count: 13 strategic contacted = Insight (#14) + Party B (#15) + Party A (re-contacted; first contact #1) + these 10. Three of the 13 did not sign NDAs (unnamed, never entered). Target-initiated.</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>10 of which (including Party A, Party B and Insight) signed a non-disclosure agreement, in each case with a standstill clause (p. 28)</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
+          <t>“Beginning June 6, Raymond James contacted 13 strategic acquirers (including Party A, Party B and Insight), 10 of which (including Party A, Party B and Insight) signed” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="n"/>
       <c r="S17" s="2" t="n"/>
       <c r="T17" s="4" t="n">
         <v>42527</v>
@@ -1588,7 +1584,7 @@
       <c r="U17" s="4" t="n">
         <v>42527</v>
       </c>
-      <c r="V17" s="4" t="n"/>
+      <c r="V17" s="2" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1596,61 +1592,59 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>later in June 2016</t>
+          <t>June 2016 or later</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14 financial sponsors contacted (incl. Party C)</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H18" s="3" t="n"/>
-      <c r="I18" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
       <c r="M18" s="2" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="N18" s="2" t="n"/>
       <c r="O18" s="2" t="n"/>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>Target-initiated contact by Raymond James after the 06/06 start of strategic outreach; 13 of the 14 signed NDAs.</t>
+          <t>Entry. NDA with a standstill ending on announcement of certain transactions; execution date not stated (after the 06/06 outreach began). Insight had an executive presentation on 06/28/2016.</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>Later in June, Raymond James also contacted 14 financial sponsors (including Party C), 13 of which (including Party C) signed a non-disclosure agreement (p. 28)</t>
+          <t>“10 of which (including Party A, Party B and Insight) signed a non-disclosure agreement, in each case with a standstill clause” (p. 28)</t>
         </is>
       </c>
       <c r="R18" s="2" t="n"/>
       <c r="S18" s="2" t="n"/>
       <c r="T18" s="4" t="n">
-        <v>42539</v>
+        <v>42527</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>42528</v>
-      </c>
-      <c r="V18" s="4" t="n">
-        <v>42551</v>
-      </c>
+        <v>42527</v>
+      </c>
+      <c r="V18" s="2" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -1658,17 +1652,17 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>later in June 2016 or after</t>
+          <t>June 2016 or later</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>13 financial NDA signers (incl. Party C)</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1680,37 +1674,37 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H19" s="3" t="n"/>
-      <c r="I19" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H19" s="2" t="n"/>
+      <c r="I19" s="2" t="n"/>
       <c r="J19" s="2" t="n"/>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="2" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="N19" s="2" t="n"/>
       <c r="O19" s="2" t="n"/>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>NDAs with standstills ending on announcement. Execution dates not given; lower bound is the start of sponsor contacts. p.36 gives the process total: 23 of 27 contacted signed (10 strategic + 13 financial).</t>
+          <t>Entry. NDA with a standstill ending on announcement of certain transactions; execution date not stated (after the 06/06 outreach began).</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>Later in June, Raymond James also contacted 14 financial sponsors (including Party C), 13 of which (including Party C) signed a non-disclosure agreement (p. 28)</t>
+          <t>“10 of which (including Party A, Party B and Insight) signed a non-disclosure agreement, in each case with a standstill clause” (p. 28)</t>
         </is>
       </c>
       <c r="R19" s="2" t="n"/>
       <c r="S19" s="2" t="n"/>
       <c r="T19" s="4" t="n">
-        <v>42539</v>
+        <v>42527</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>42528</v>
-      </c>
-      <c r="V19" s="4" t="n"/>
+        <v>42527</v>
+      </c>
+      <c r="V19" s="2" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1718,59 +1712,59 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>before 07/18/2016</t>
+          <t>June 2016 or later</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n"/>
+          <t>7 other strategic NDA signers</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Deadline set</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="3" t="n"/>
-      <c r="I20" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H20" s="2" t="n"/>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
-      <c r="M20" s="2" t="n"/>
+      <c r="M20" s="2" t="n">
+        <v>7</v>
+      </c>
       <c r="N20" s="2" t="n"/>
       <c r="O20" s="2" t="n"/>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>Raymond James told the interested parties that initial indications of interest (IOIs) were due 07/18/2016 from strategic buyers and 07/21/2016 from financial sponsors. When this was communicated is not stated.</t>
+          <t>Entry. Count: 10 strategic NDA signers = Insight (#17) + Party B (#18) + Party A (NDA #6; the filing counts it among the 10, without saying whether a new June instrument was signed) + these 7.</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>Raymond James also communicated to the interested parties that initial indications of interest were due on July 18, 2016 from strategic buyers and July 21, 2016 from financial sponsors (p. 29)</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>“10 of which (including Party A, Party B and Insight) signed a non-disclosure agreement, in each case with a standstill clause” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
       <c r="T20" s="4" t="n">
-        <v>42548</v>
+        <v>42527</v>
       </c>
       <c r="U20" s="4" t="n">
         <v>42527</v>
       </c>
-      <c r="V20" s="4" t="n">
-        <v>42569</v>
-      </c>
+      <c r="V20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1778,54 +1772,60 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>06/21/2016 to 07/07/2016</t>
+          <t>later in June 2016</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H21" s="3" t="n"/>
-      <c r="I21" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H21" s="2" t="n"/>
+      <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
+      <c r="M21" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="n"/>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>Information access: management gave executive presentations to eight parties that had expressed interest (Insight on 06/28/2016); the other NDA signers are not reported as receiving one. The other seven are not named.</t>
+          <t>Target-initiated contact by Raymond James in the financial-sponsor outreach, 'later in June' (after 06/06). Party C is a financial sponsor (p. 30).</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>our management team participated in executive presentations with eight parties that had expressed an interest in acquiring us (p. 29)</t>
+          <t>“Later in June, Raymond James also contacted 14 financial sponsors (including Party C), 13 of which (including Party C) signed a non-disclosure agreement” (p. 28)</t>
         </is>
       </c>
       <c r="R21" s="2" t="n"/>
       <c r="S21" s="2" t="n"/>
       <c r="T21" s="4" t="n">
-        <v>42550</v>
+        <v>42539</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>42542</v>
+        <v>42528</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>42558</v>
+        <v>42551</v>
       </c>
     </row>
     <row r="22">
@@ -1834,76 +1834,60 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>by 07/27/2016 (due 07/18/2016)</t>
+          <t>later in June 2016</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>13 other financial sponsors contacted</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H22" s="3" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H22" s="2" t="n"/>
+      <c r="I22" s="2" t="n"/>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
+      <c r="L22" s="2" t="n"/>
       <c r="M22" s="2" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="2" t="n"/>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>Unclear: Raymond James reviewed 'conditions and significant open diligence items' across the IOIs, not per bidder. Highest initial IOI. Arrival undated; reviewed by the board 07/27. Ref: $7.82 close 07/27/2016.</t>
+          <t>Count: 14 financial sponsors contacted = Party C (#20) + these 13. One of the 14 did not sign an NDA (unnamed, never entered). Target-initiated.</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>The highest price included in an initial indication of interest was submitted by Insight, with a range of $10.75-11.75 per share. (p. 29)</t>
+          <t>“Later in June, Raymond James also contacted 14 financial sponsors (including Party C), 13 of which (including Party C) signed a non-disclosure agreement” (p. 28)</t>
         </is>
       </c>
       <c r="R22" s="2" t="n"/>
       <c r="S22" s="2" t="n"/>
       <c r="T22" s="4" t="n">
-        <v>42569</v>
+        <v>42539</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>42527</v>
+        <v>42528</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>42578</v>
+        <v>42551</v>
       </c>
     </row>
     <row r="23">
@@ -1912,51 +1896,35 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>by 07/27/2016 (due 07/18/2016)</t>
+          <t>June 2016 or later</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H23" s="3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="I23" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H23" s="2" t="n"/>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="2" t="n">
         <v>1</v>
       </c>
@@ -1964,25 +1932,23 @@
       <c r="O23" s="2" t="n"/>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>Unclear: conditions and open diligence were reviewed across the IOIs, not per bidder. Later called Party B's 'initial verbal indication of interest' (p.30). Arrival undated.</t>
+          <t>Entry. NDA with a standstill ending on announcement of certain transactions; execution date not stated (after its later-June contact).</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>Party B submitted a range of $10.50-11.00 per share (p. 29)</t>
+          <t>“13 of which (including Party C) signed a non-disclosure agreement, in each case with a standstill clause” (p. 28)</t>
         </is>
       </c>
       <c r="R23" s="2" t="n"/>
       <c r="S23" s="2" t="n"/>
       <c r="T23" s="4" t="n">
-        <v>42569</v>
+        <v>42539</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>42527</v>
-      </c>
-      <c r="V23" s="4" t="n">
-        <v>42578</v>
-      </c>
+        <v>42528</v>
+      </c>
+      <c r="V23" s="2" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1990,59 +1956,59 @@
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>07/18/2016</t>
+          <t>June 2016 or later</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n"/>
+          <t>12 other financial NDA signers</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>NDA signed</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H24" s="3" t="n"/>
-      <c r="I24" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H24" s="2" t="n"/>
+      <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
+      <c r="M24" s="2" t="n">
+        <v>12</v>
+      </c>
       <c r="N24" s="2" t="n"/>
       <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>IOI due date for strategic buyers. The board acted on the IOIs in hand on 07/27 (Enforced).</t>
+          <t>Entry. Count: 13 financial NDA signers = Party C (#22) + these 12. Filing's overall total: 27 approached, 23 NDAs (p. 36).</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>initial indications of interest were due on July 18, 2016 from strategic buyers (p. 29)</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>“13 of which (including Party C) signed a non-disclosure agreement, in each case with a standstill clause” (p. 28)</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="n"/>
       <c r="S24" s="2" t="n"/>
       <c r="T24" s="4" t="n">
-        <v>42569</v>
+        <v>42539</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>42569</v>
-      </c>
-      <c r="V24" s="4" t="n">
-        <v>42569</v>
-      </c>
+        <v>42528</v>
+      </c>
+      <c r="V24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -2050,70 +2016,60 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>by 07/18/2016</t>
+          <t>06/21/2016 to 07/07/2016</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>5 strategic NDA signers without an IOI</t>
+          <t>8 interested parties (incl. Insight)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H25" s="2" t="n"/>
+      <c r="I25" s="2" t="n"/>
       <c r="J25" s="2" t="n"/>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="n"/>
       <c r="M25" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="N25" s="2" t="n"/>
+      <c r="O25" s="2" t="n"/>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>Count: 5 = 10 strategic NDA signers − Party A (03/29 proposal counted as its IOI) − Insight − Party B − 2 unnamed strategic submitters. Assumes each IOI submitter was an NDA signer (Q5). Reasons not given.</t>
+          <t>Information access: management gave executive presentations to eight parties that had expressed interest (Insight on 06/28), out of 23 NDA signers; the other seven are unnamed. Limited diligence requests answered through July.</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>Four strategic parties (in addition to Party A, which submitted the proposal described above on March 29, 2016), including Insight and Party B, and five financial sponsors, including Party C (p. 29)</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“Beginning on June 21, 2016 through July 7, 2016, our management team participated in executive presentations with eight parties that had expressed an interest in acquiring us” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="n"/>
       <c r="S25" s="2" t="n"/>
       <c r="T25" s="4" t="n">
-        <v>42569</v>
-      </c>
-      <c r="U25" s="4" t="n"/>
+        <v>42550</v>
+      </c>
+      <c r="U25" s="4" t="n">
+        <v>42542</v>
+      </c>
       <c r="V25" s="4" t="n">
-        <v>42569</v>
+        <v>42558</v>
       </c>
     </row>
     <row r="26">
@@ -2122,76 +2078,58 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>by 07/27/2016 (due 07/21/2016)</t>
+          <t>June-July 2016 (not dated)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline set</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H26" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I26" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Informal</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>Unclear</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H26" s="2" t="n"/>
+      <c r="I26" s="2" t="n"/>
+      <c r="J26" s="2" t="n"/>
+      <c r="K26" s="2" t="n"/>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
       <c r="N26" s="2" t="n"/>
       <c r="O26" s="2" t="n"/>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>Unclear: conditions and open diligence were reviewed across the IOIs, not per bidder. Point price. Arrival undated.</t>
+          <t>Raymond James told interested parties that initial indications of interest were due 07/18/2016 (strategic) and 07/21/2016 (financial sponsors). Communication date not stated; bounded by the round opening and the first due date.</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>Party C submitted a price of $11.00 per share (p. 29)</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="n"/>
+          <t>“Raymond James also communicated to the interested parties that initial indications of interest were due on July 18, 2016 from strategic buyers and July 21, 2016 from financial sponsors” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
       <c r="S26" s="2" t="n"/>
       <c r="T26" s="4" t="n">
-        <v>42572</v>
+        <v>42550</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>42528</v>
+        <v>42527</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>42578</v>
+        <v>42569</v>
       </c>
     </row>
     <row r="27">
@@ -2200,17 +2138,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>by 07/27/2016 (due 07/18 and 07/21/2016)</t>
+          <t>by 07/27/2016 (due 07/18/2016)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>6 other IOI submitters (2 strategic, 4 financial)</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -2222,13 +2160,13 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>8.800000000000001</v>
+        <v>10.75</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>10.5</v>
+        <v>11.75</v>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
@@ -2246,28 +2184,24 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N27" s="2" t="n"/>
       <c r="O27" s="2" t="n"/>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>Unclear: conditions differ within the cohort and are not reported by bidder. Count 6 = 4 strategic submitters − Insight − Party B, plus 5 financial − Party C. The $8.80–$10.50 range covers all six IOIs; the filing gives no price by bidder.</t>
+          <t>Unclear: the board reviewed 'conditions and significant open diligence items' for the IOIs without per-bidder detail. Highest-priced initial indication, range $10.75-$11.75. Arrival not dated; sorted at the strategic due date. Ref: $7.82 close 07/27/2016.</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>The other initial indications of interest included prices from a low of $8.80 per share to a high of $10.50 per share. (p. 29)</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>Q5</t>
-        </is>
-      </c>
+          <t>“The highest price included in an initial indication of interest was submitted by Insight, with a range of $10.75-11.75 per share” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="n"/>
       <c r="S27" s="2" t="n"/>
       <c r="T27" s="4" t="n">
-        <v>42572</v>
+        <v>42569</v>
       </c>
       <c r="U27" s="4" t="n">
         <v>42527</v>
@@ -2282,58 +2216,76 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>07/21/2016</t>
+          <t>by 07/27/2016 (due 07/18/2016)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H28" s="3" t="n"/>
-      <c r="I28" s="3" t="n"/>
-      <c r="J28" s="2" t="n"/>
-      <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
-      <c r="M28" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N28" s="2" t="n"/>
       <c r="O28" s="2" t="n"/>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>IOI due date for financial sponsors. The board acted on the IOIs in hand on 07/27 (Enforced).</t>
+          <t>Unclear: IOI conditions reviewed only collectively. Initial indication of $10.50-$11.00, given verbally (p. 30). Arrival not dated; sorted at the strategic due date.</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>July 21, 2016 from financial sponsors (p. 29)</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>Q4</t>
-        </is>
-      </c>
+          <t>“Party B submitted a range of $10.50-11.00 per share” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="n"/>
       <c r="S28" s="2" t="n"/>
       <c r="T28" s="4" t="n">
-        <v>42572</v>
+        <v>42569</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>42572</v>
+        <v>42527</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>42572</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="29">
@@ -2342,70 +2294,58 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>by 07/21/2016</t>
+          <t>07/18/2016</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8 financial NDA signers without an IOI</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="3" t="n"/>
-      <c r="I29" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H29" s="2" t="n"/>
+      <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
-      <c r="M29" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M29" s="2" t="n"/>
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>Count: 8 = 13 financial NDA signers − Party C − 4 unnamed financial submitters. Assumes each IOI submitter was an NDA signer (Q5). Reasons not given.</t>
+          <t>Strategic buyers' IOI due date reached. Next step was the 07/27 board review and selection of five on the IOIs in hand (Enforced).</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>Four strategic parties (in addition to Party A, which submitted the proposal described above on March 29, 2016), including Insight and Party B, and five financial sponsors, including Party C (p. 29)</t>
+          <t>“initial indications of interest were due on July 18, 2016 from strategic buyers” (p. 29)</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S29" s="2" t="n"/>
       <c r="T29" s="4" t="n">
-        <v>42572</v>
-      </c>
-      <c r="U29" s="4" t="n"/>
+        <v>42569</v>
+      </c>
+      <c r="U29" s="4" t="n">
+        <v>42569</v>
+      </c>
       <c r="V29" s="4" t="n">
-        <v>42572</v>
+        <v>42569</v>
       </c>
     </row>
     <row r="30">
@@ -2414,58 +2354,70 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>07/27/2016</t>
+          <t>by 07/18/2016</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n"/>
+          <t>5 strategic NDA signers without IOIs</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="3" t="n"/>
-      <c r="I30" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H30" s="2" t="n"/>
+      <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
-      <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n"/>
+      <c r="M30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>Board advances the five highest-priced IOIs: Insight, Party B, Party C and two unnamed parties. All five got management presentations (08/04–08/15/2016), more diligence material and meetings in August. Not final.</t>
+          <t>Count: 10 strategic NDA signers - 4 strategic IOI submitters (incl. Insight, Party B) - Party A (standing 03/29 proposal counted as its IOI) = 5. No earlier exits. Unnamed.</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>our board directed our management and the Raymond James team to continue to pursue a transaction with the five parties that submitted the highest-priced initial indications of interest (p. 29)</t>
+          <t>“Four strategic parties (in addition to Party A, which submitted the proposal described above on March 29, 2016), including Insight and Party B, and five financial sponsors” (p. 29)</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>Q1</t>
+          <t>Q2; Q4</t>
         </is>
       </c>
       <c r="S30" s="2" t="n"/>
       <c r="T30" s="4" t="n">
-        <v>42578</v>
-      </c>
-      <c r="U30" s="4" t="n">
-        <v>42578</v>
-      </c>
+        <v>42569</v>
+      </c>
+      <c r="U30" s="2" t="n"/>
       <c r="V30" s="4" t="n">
-        <v>42578</v>
+        <v>42569</v>
       </c>
     </row>
     <row r="31">
@@ -2474,12 +2426,12 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>by 07/27/2016</t>
+          <t>by 07/27/2016 (due 07/18 or 07/21/2016)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5 IOI submitters not selected</t>
+          <t>6 other IOI submitters (2 strategic, 4 financial)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2489,53 +2441,63 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="3" t="n"/>
-      <c r="I31" s="3" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
       <c r="M31" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="N31" s="2" t="n"/>
+      <c r="O31" s="2" t="n"/>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>Count: 5 = 10 IOIs considered (9 new + Party A's 03/29 proposal) − 5 advanced. Selection was by price: highest five advanced. Members unnamed; Party A may be here or among the two unnamed advancers (Q3).</t>
+          <t>Unclear: IOI conditions reviewed only collectively. Count: 9 new IOIs (4 strategic incl. Insight, Party B; 5 financial incl. Party C) less those three = 6 (2 strategic, 4 financial; range not split by type). Range stated for 'the other' IOIs; may also describe Party A's $10.30 floor.</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>our board directed our management and the Raymond James team to continue to pursue a transaction with the five parties that submitted the highest-priced initial indications of interest (p. 29)</t>
+          <t>“The other initial indications of interest included prices from a low of $8.80 per share to a high of $10.50 per share” (p. 29)</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>Q3</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S31" s="2" t="n"/>
       <c r="T31" s="4" t="n">
-        <v>42578</v>
-      </c>
-      <c r="U31" s="4" t="n"/>
+        <v>42572</v>
+      </c>
+      <c r="U31" s="4" t="n">
+        <v>42527</v>
+      </c>
       <c r="V31" s="4" t="n">
         <v>42578</v>
       </c>
@@ -2546,58 +2508,76 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>08/05/2016 to 08/15/2016</t>
+          <t>by 07/27/2016 (due 07/21/2016)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="3" t="n"/>
-      <c r="I32" s="3" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Informal</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Unclear</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N32" s="2" t="n"/>
       <c r="O32" s="2" t="n"/>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Information access: Raymond James emailed the draft merger agreement to Party B (08/05), Insight (08/09) and Party C (08/15/2016); no draft is reported for the two other advanced parties. FaegreBD also held August calls with counsel for these three.</t>
+          <t>Unclear: IOI conditions reviewed only collectively. Initial indication at a point price of $11.00. Arrival not dated; sorted at the financial due date.</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>provided a draft of the merger agreement by email to Party B on August 5, 2016, to Insight on August 9, 2016, and to Party C on August 15 (p. 29)</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
+          <t>“Party C submitted a price of $11.00 per share” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="n"/>
       <c r="S32" s="2" t="n"/>
       <c r="T32" s="4" t="n">
-        <v>42592</v>
+        <v>42572</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>42587</v>
+        <v>42528</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>42597</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="33">
@@ -2606,7 +2586,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>08/16/2016</t>
+          <t>07/21/2016</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2617,17 +2597,17 @@
       <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H33" s="3" t="n"/>
-      <c r="I33" s="3" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="H33" s="2" t="n"/>
+      <c r="I33" s="2" t="n"/>
       <c r="J33" s="2" t="n"/>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
@@ -2636,28 +2616,28 @@
       <c r="O33" s="2" t="n"/>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>Final-proposal instruction letters to Insight, Party B and Party C: proposals due 5:00 p.m. ET 08/30/2016 with a merger-agreement mark-up. No letter reported to the two other advanced parties (Q6). Announced as final.</t>
+          <t>Financial sponsors' IOI due date reached. Next step was the 07/27 board review and selection of five on the IOIs in hand (Enforced).</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>Raymond James provided each of Insight, Party B and Party C with an instruction letter relating to their final proposals. (p. 29)</t>
+          <t>“July 21, 2016 from financial sponsors” (p. 29)</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>Q1; Q6</t>
+          <t>Q3</t>
         </is>
       </c>
       <c r="S33" s="2" t="n"/>
       <c r="T33" s="4" t="n">
-        <v>42598</v>
+        <v>42572</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>42598</v>
+        <v>42572</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>42598</v>
+        <v>42572</v>
       </c>
     </row>
     <row r="34">
@@ -2666,80 +2646,70 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>08/30/2016</t>
+          <t>by 07/21/2016</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>8 financial NDA signers without IOIs</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="H34" s="2" t="n"/>
+      <c r="I34" s="2" t="n"/>
+      <c r="J34" s="2" t="n"/>
+      <c r="K34" s="2" t="n"/>
+      <c r="L34" s="2" t="n"/>
+      <c r="M34" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>Heavy: requires 30 days of exclusivity to sign, needs debt financing (reverse termination fee as sole remedy), third-party diligence calls. Negotiated commitment letters supplied. Mark-up added a financing structure that could delay closing.</t>
+          <t>Count: 13 financial NDA signers - 5 financial IOI submitters (incl. Party C) = 8. No earlier exits. Unnamed.</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>Party B offered a price of $12.00 per share and indicated that it expected to be able to execute a definitive merger agreement within 30 days (p. 29)</t>
+          <t>“Four strategic parties (in addition to Party A, which submitted the proposal described above on March 29, 2016), including Insight and Party B, and five financial sponsors” (p. 29)</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q4</t>
         </is>
       </c>
       <c r="S34" s="2" t="n"/>
       <c r="T34" s="4" t="n">
-        <v>42612</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>42612</v>
-      </c>
+        <v>42572</v>
+      </c>
+      <c r="U34" s="2" t="n"/>
       <c r="V34" s="4" t="n">
-        <v>42612</v>
+        <v>42572</v>
       </c>
     </row>
     <row r="35">
@@ -2748,80 +2718,70 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>08/30/2016</t>
+          <t>by 07/27/2016</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>5 IOI holders not advanced (from Party A and 6 unnamed)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H35" s="2" t="n"/>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
       <c r="M35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" s="2" t="n"/>
-      <c r="O35" s="2" t="n"/>
+        <v>5</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>Lower offer than rivals</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>Heavy: needs 30–45 days after exclusivity to sign; 'still exploring third-party financing' (no commitment reported); third-party diligence calls. Mark-up had no financing contingency or reverse termination fee.</t>
+          <t>Count: 10 IOI holders (9 new + Party A's standing proposal) - 5 advanced = 5, drawn from the 6 unnamed submitters (#30) and Party A; Party A may be among them or among the two unnamed advancers. The five kept were the highest-priced.</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>Party C offered a price of $11.00 per share and indicated that it expected to be able to execute a definitive merger agreement within 30 to 45 days (p. 30)</t>
+          <t>“continue to pursue a transaction with the five parties that submitted the highest-priced initial indications of interest, including Insight, Party B and Party C” (p. 29)</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q2; Q4</t>
         </is>
       </c>
       <c r="S35" s="2" t="n"/>
       <c r="T35" s="4" t="n">
-        <v>42612</v>
-      </c>
-      <c r="U35" s="4" t="n">
-        <v>42612</v>
-      </c>
+        <v>42578</v>
+      </c>
+      <c r="U35" s="2" t="n"/>
       <c r="V35" s="4" t="n">
-        <v>42612</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="36">
@@ -2830,7 +2790,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/30/2016</t>
+          <t>07/27/2016</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2841,17 +2801,17 @@
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Deadline</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H36" s="3" t="n"/>
-      <c r="I36" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="H36" s="2" t="n"/>
+      <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
@@ -2860,28 +2820,28 @@
       <c r="O36" s="2" t="n"/>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>Final-proposal due date (5:00 p.m. ET). Party B and Party C met it; Insight's proposal arrived 08/31 and was considered (Late bids accepted).</t>
+          <t>Board reviewed the 10 IOIs and advanced the five highest-priced: Insight, Party B, Party C and two unnamed (types unknown; possibly incl. Party A). All five got management presentations 08/04-08/15 and additional diligence materials in August. No offers requested yet.</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>The letter instructed each party to submit its proposal by 5:00 p.m. Eastern time on August 30, 2016 (p. 29)</t>
+          <t>“our board directed our management and the Raymond James team to continue to pursue a transaction with the five parties that submitted the highest-priced initial indications of interest” (p. 29)</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>Q8</t>
+          <t>Q1; Q2</t>
         </is>
       </c>
       <c r="S36" s="2" t="n"/>
       <c r="T36" s="4" t="n">
-        <v>42612</v>
+        <v>42578</v>
       </c>
       <c r="U36" s="4" t="n">
-        <v>42612</v>
+        <v>42578</v>
       </c>
       <c r="V36" s="4" t="n">
-        <v>42612</v>
+        <v>42578</v>
       </c>
     </row>
     <row r="37">
@@ -2890,80 +2850,54 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/31/2016</t>
+          <t>08/05/2016 to 08/15/2016</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="H37" s="2" t="n"/>
+      <c r="I37" s="2" t="n"/>
+      <c r="J37" s="2" t="n"/>
+      <c r="K37" s="2" t="n"/>
+      <c r="L37" s="2" t="n"/>
+      <c r="M37" s="2" t="n"/>
       <c r="N37" s="2" t="n"/>
       <c r="O37" s="2" t="n"/>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>Heavy: mark-up added a closing condition on continued employment of certain individuals; 30 days of exclusivity required to sign. No new financing needed. Termination fee raised to 4.0% of EV. Submitted one day after the due date.</t>
+          <t>Information access: Raymond James emailed the draft merger agreement to Party B (08/05), Insight (08/09) and Party C (08/15); no draft is reported for the two unnamed round-2 participants. FaegreBD held August calls with the three bidders' counsel.</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>Insight offered a price of $11.75 per share and indicated that it expected to be able to execute a definitive merger agreement within 30 days (p. 30)</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr">
-        <is>
-          <t>Q7; Q8</t>
-        </is>
-      </c>
+          <t>“Raymond James provided a draft of the merger agreement by email to Party B on August 5, 2016, to Insight on August 9, 2016, and to Party C” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="n"/>
       <c r="S37" s="2" t="n"/>
       <c r="T37" s="4" t="n">
-        <v>42613</v>
+        <v>42587</v>
       </c>
       <c r="U37" s="4" t="n">
-        <v>42613</v>
+        <v>42587</v>
       </c>
       <c r="V37" s="4" t="n">
-        <v>42613</v>
+        <v>42597</v>
       </c>
     </row>
     <row r="38">
@@ -2972,7 +2906,7 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>08/31/2016</t>
+          <t>08/16/2016</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2983,17 +2917,17 @@
       <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H38" s="3" t="n"/>
-      <c r="I38" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H38" s="2" t="n"/>
+      <c r="I38" s="2" t="n"/>
       <c r="J38" s="2" t="n"/>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
@@ -3002,24 +2936,28 @@
       <c r="O38" s="2" t="n"/>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>Improvement requests from Raymond James: Party B warned about financing risk and delay and sounded out on raising $12.00; Party C told its price was not competitive and asked to clarify financing; Insight told its price was not competitive and asked to drop the employment condition.</t>
+          <t>Final round: Raymond James sent Insight, Party B and Party C instruction letters for final proposals, due 5:00 p.m. ET 08/30/2016 with a merger-agreement mark-up; later called 'best and final' (p. 36). Letters to the two unnamed participants not reported; both counted as not submitting.</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>Our management instructed Raymond James to contact each of the three parties to suggest they make certain initial improvements to their proposals in order to make them more competitive (p. 30)</t>
-        </is>
-      </c>
-      <c r="R38" s="2" t="n"/>
+          <t>“The letter instructed each party to submit its proposal by 5:00 p.m. Eastern time on August 30, 2016, and, among other items, to include a mark-up of the merger agreement” (p. 29)</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="n"/>
       <c r="T38" s="4" t="n">
-        <v>42613</v>
+        <v>42598</v>
       </c>
       <c r="U38" s="4" t="n">
-        <v>42613</v>
+        <v>42598</v>
       </c>
       <c r="V38" s="4" t="n">
-        <v>42613</v>
+        <v>42598</v>
       </c>
     </row>
     <row r="39">
@@ -3028,12 +2966,12 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>08/31/2016 to 09/01/2016</t>
+          <t>08/30/2016</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3050,13 +2988,13 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>11.75</v>
+        <v>12</v>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3080,28 +3018,28 @@
       <c r="O39" s="2" t="n"/>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>Heavy: still requires 30 days of exclusivity. Revision: agrees to delete the continued-employment closing condition, as reported to the 09/01 board; price unchanged at $11.75 (#36).</t>
+          <t>Heavy: needed debt financing with a reverse termination fee as the target's sole remedy (negotiated commitment letters supplied), contingent on third-party diligence calls, and 30 days of exclusivity to sign. Merger-agreement mark-up submitted. Board saw $12.00 as a big rise from its verbal IOI.</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>Raymond James advised that Insight had agreed to delete the closing condition relating to continued employment of certain individuals. (p. 30)</t>
+          <t>“Party B offered a price of $12.00 per share and indicated that it expected to be able to execute a definitive merger agreement within 30 days” (p. 29)</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S39" s="2" t="n"/>
       <c r="T39" s="4" t="n">
-        <v>42613</v>
+        <v>42612</v>
       </c>
       <c r="U39" s="4" t="n">
-        <v>42613</v>
+        <v>42612</v>
       </c>
       <c r="V39" s="4" t="n">
-        <v>42614</v>
+        <v>42612</v>
       </c>
     </row>
     <row r="40">
@@ -3110,17 +3048,17 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>08/31/2016 to 09/01/2016</t>
+          <t>08/30/2016</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
@@ -3132,13 +3070,13 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3162,28 +3100,28 @@
       <c r="O40" s="2" t="n"/>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>Heavy: 30-day exclusivity, debt financing with reverse termination fee as sole remedy, third-party diligence calls still stand. Revised after feedback to eliminate or reduce financing delays; price unchanged at $12.00 (#33).</t>
+          <t>Heavy: still exploring third-party financing (uncommitted), contingent on third-party diligence calls, and 30-45 days of exclusivity to sign. Mark-up had no financing contingency or reverse termination fee.</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>Party B had, in response to initial feedback, revised its proposal to eliminate or reduce the delays associated with their financing. (p. 30)</t>
+          <t>“Party C offered a price of $11.00 per share and indicated that it expected to be able to execute a definitive merger agreement within 30 to 45 days” (p. 30)</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S40" s="2" t="n"/>
       <c r="T40" s="4" t="n">
-        <v>42613</v>
+        <v>42612</v>
       </c>
       <c r="U40" s="4" t="n">
-        <v>42613</v>
+        <v>42612</v>
       </c>
       <c r="V40" s="4" t="n">
-        <v>42614</v>
+        <v>42612</v>
       </c>
     </row>
     <row r="41">
@@ -3192,80 +3130,58 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>08/31/2016 to 09/01/2016</t>
+          <t>08/30/2016</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H41" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H41" s="2" t="n"/>
+      <c r="I41" s="2" t="n"/>
+      <c r="J41" s="2" t="n"/>
+      <c r="K41" s="2" t="n"/>
+      <c r="L41" s="2" t="n"/>
+      <c r="M41" s="2" t="n"/>
       <c r="N41" s="2" t="n"/>
       <c r="O41" s="2" t="n"/>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>Heavy: 30–45-day post-exclusivity signing period and diligence calls carried from #34; no financing commitment reported. Raises to $11.25 and agrees to leave any financing contingency out of the merger agreement.</t>
+          <t>Final-proposal due date (5:00 p.m. ET). Party B and Party C submitted on it; Insight submitted on 08/31 (#41) and the target reviewed and negotiated on its bid (Late bids accepted). The two unnamed participants did not submit.</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Party C had updated its proposal and increased its price to $11.25 per share and agreed not to include any financing contingency in the merger agreement. (p. 30)</t>
+          <t>“submit its proposal by 5:00 p.m. Eastern time on August 30, 2016” (p. 29)</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="S41" s="2" t="n"/>
       <c r="T41" s="4" t="n">
-        <v>42613</v>
+        <v>42612</v>
       </c>
       <c r="U41" s="4" t="n">
-        <v>42613</v>
+        <v>42612</v>
       </c>
       <c r="V41" s="4" t="n">
-        <v>42614</v>
+        <v>42612</v>
       </c>
     </row>
     <row r="42">
@@ -3274,54 +3190,80 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>09/01/2016</t>
+          <t>08/31/2016</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
+          <t>Insight Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H42" s="3" t="n"/>
-      <c r="I42" s="3" t="n"/>
-      <c r="J42" s="2" t="n"/>
-      <c r="K42" s="2" t="n"/>
-      <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="2" t="n"/>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>Preferred bidder: board directs further negotiation of Insight's terms before considering its 30-day exclusivity request. It judged Party B's financing and diligence requests problematic and Party C's price and financing weaker. Raymond James reported two of the five had not submitted.</t>
+          <t>Heavy: mark-up added a closing condition on continued employment of unspecified individuals; 30 days of exclusivity sought to sign. No new financing needed. Mark-up raised termination fee from 2.5% to 4.0% of EV. Submitted a day after the 08/30 due date.</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>our board directed our management and our advisors to further negotiate terms of the Insight proposal before our board would consider Insight's request for a 30-day exclusivity period (p. 31)</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="n"/>
+          <t>“Insight offered a price of $11.75 per share and indicated that it expected to be able to execute a definitive merger agreement within 30 days” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Q5; Q6</t>
+        </is>
+      </c>
       <c r="S42" s="2" t="n"/>
       <c r="T42" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
       <c r="U42" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
       <c r="V42" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
     </row>
     <row r="43">
@@ -3330,67 +3272,55 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>after 09/01/2016</t>
+          <t>08/31/2016</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>2 unnamed advanced parties</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Did not submit</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H43" s="3" t="n"/>
-      <c r="I43" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H43" s="2" t="n"/>
+      <c r="I43" s="2" t="n"/>
       <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
-      <c r="M43" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N43" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
+      <c r="M43" s="2" t="n"/>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="2" t="n"/>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>Reported: at the 09/01 board these two remained in the process without final proposals, still deciding; both later decided not to submit. Decision undated. One could be Party A (#30). Reason not given.</t>
+          <t>Improvement requests: management had Raymond James ask Party B to address financing risk and delay and gauge a raise above $12.00, tell Party C its price was not competitive and seek financing clarity, and tell Insight its price was not competitive and ask it to drop the employment condition.</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>Both parties ultimately determined not to submit proposals. (p. 31)</t>
-        </is>
-      </c>
-      <c r="R43" s="2" t="inlineStr">
-        <is>
-          <t>Q3; Q6</t>
-        </is>
-      </c>
+          <t>“Our management instructed Raymond James to contact each of the three parties to suggest they make certain initial improvements to their proposals” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="n"/>
       <c r="S43" s="2" t="n"/>
       <c r="T43" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
       <c r="U43" s="4" t="n">
-        <v>42614</v>
-      </c>
-      <c r="V43" s="4" t="n"/>
+        <v>42613</v>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>42613</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
@@ -3398,51 +3328,77 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>09/01/2016</t>
+          <t>08/31/2016 to 09/01/2016</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Sullivan &amp; Cromwell LLP</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="n"/>
+          <t>Insight Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Adviser</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="n"/>
-      <c r="J44" s="2" t="n"/>
-      <c r="K44" s="2" t="n"/>
-      <c r="L44" s="2" t="n"/>
-      <c r="M44" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="2" t="n"/>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>Insight's legal counsel; earliest shown acting 09/01/2016, negotiating merger-agreement terms with FaegreBD.</t>
+          <t>Heavy: still sought 30 days of exclusivity to sign, with diligence items open. Revised terms, price unchanged (carried from #41): agreed to delete the continued-employment closing condition, reported at the 09/01 board meeting.</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>FaegreBD contacted representatives of Sullivan &amp; Cromwell LLP, Insight's legal counsel, to discuss certain terms in Insight's proposed merger agreement. (p. 31)</t>
-        </is>
-      </c>
-      <c r="R44" s="2" t="n"/>
+          <t>“Raymond James advised that Insight had agreed to delete the closing condition relating to continued employment of certain individuals” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S44" s="2" t="n"/>
       <c r="T44" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
       <c r="U44" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
       <c r="V44" s="4" t="n">
         <v>42614</v>
@@ -3454,12 +3410,12 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>09/01/2016</t>
+          <t>08/31/2016 to 09/01/2016</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Party B</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3476,7 +3432,7 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>12</v>
@@ -3506,25 +3462,25 @@
       <c r="O45" s="2" t="n"/>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>Heavy: 30 days of exclusivity still required; Insight refused 20 days on 09/02. Raises from $11.75 (#38) after being told its price was not competitive. Termination fee then negotiated from 4.0% to 3.5% of EV. Ref: $9.98 close 09/01/2016.</t>
+          <t>Heavy: still needed financing with a reverse termination fee as sole remedy and third-party diligence calls. After feedback, revised its financing terms to eliminate or reduce related delays; price unchanged (carried from #38).</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>On September 1, 2016, Insight increased its offer price to $12.00 per share. (p. 31)</t>
+          <t>“Party B had, in response to initial feedback, revised its proposal to eliminate or reduce the delays associated with their financing” (p. 30)</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S45" s="2" t="n"/>
       <c r="T45" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
       <c r="U45" s="4" t="n">
-        <v>42614</v>
+        <v>42613</v>
       </c>
       <c r="V45" s="4" t="n">
         <v>42614</v>
@@ -3536,35 +3492,51 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>09/02/2016</t>
+          <t>08/31/2016 to 09/01/2016</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H46" s="3" t="n"/>
-      <c r="I46" s="3" t="n"/>
-      <c r="J46" s="2" t="n"/>
-      <c r="K46" s="2" t="n"/>
-      <c r="L46" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M46" s="2" t="n">
         <v>1</v>
       </c>
@@ -3572,24 +3544,28 @@
       <c r="O46" s="2" t="n"/>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>Executed: board grants Insight 30 days of exclusivity (Insight would not accept 20); the agreement, signed later on 09/02, expires 11:59 p.m. ET 09/30/2016. Round 4 ends in definitive negotiation with Insight. Ref: $9.93 close 09/02/2016.</t>
+          <t>Heavy: third-party diligence calls and 30-45 days of exclusivity still required; no financing commitment reported. Raised price from $11.00 to $11.25 and agreed to no financing contingency in the merger agreement.</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>Later on September 2, 2016, the parties signed an exclusivity agreement with an expiration time of 11:59 p.m. Eastern time on September 30, 2016. (p. 31)</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="n"/>
+          <t>“Party C had updated its proposal and increased its price to $11.25 per share and agreed not to include any financing contingency in the merger agreement” (p. 30)</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S46" s="2" t="n"/>
       <c r="T46" s="4" t="n">
-        <v>42615</v>
+        <v>42613</v>
       </c>
       <c r="U46" s="4" t="n">
-        <v>42615</v>
+        <v>42613</v>
       </c>
       <c r="V46" s="4" t="n">
-        <v>42615</v>
+        <v>42614</v>
       </c>
     </row>
     <row r="47">
@@ -3598,70 +3574,54 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>by 09/02/2016</t>
+          <t>09/01/2016</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H47" s="3" t="n"/>
-      <c r="I47" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H47" s="2" t="n"/>
+      <c r="I47" s="2" t="n"/>
       <c r="J47" s="2" t="n"/>
       <c r="K47" s="2" t="n"/>
       <c r="L47" s="2" t="n"/>
-      <c r="M47" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N47" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O47" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M47" s="2" t="n"/>
+      <c r="N47" s="2" t="n"/>
+      <c r="O47" s="2" t="n"/>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>Inferred: Party B was a live rival when the target executed exclusivity with Insight (#45); no exit reported before this. Party B re-entered on 10/01 (#52).</t>
+          <t>Preferred bidder: the board saw Party B's financing and diligence terms as problematic and Party C's price and financing as weaker. It directed further negotiation of Insight's terms before considering Insight's 30-day exclusivity request, with a report due 09/02. Ref: $9.98 close.</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>Later on September 2, 2016, the parties signed an exclusivity agreement with an expiration time of 11:59 p.m. Eastern time on September 30, 2016. (p. 31)</t>
-        </is>
-      </c>
-      <c r="R47" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+          <t>“our board directed our management and our advisors to further negotiate terms of the Insight proposal before our board would consider Insight's request for a 30-day exclusivity” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="n"/>
       <c r="S47" s="2" t="n"/>
       <c r="T47" s="4" t="n">
-        <v>42615</v>
-      </c>
-      <c r="U47" s="4" t="n"/>
+        <v>42614</v>
+      </c>
+      <c r="U47" s="4" t="n">
+        <v>42614</v>
+      </c>
       <c r="V47" s="4" t="n">
-        <v>42615</v>
+        <v>42614</v>
       </c>
     </row>
     <row r="48">
@@ -3670,71 +3630,67 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>by 09/02/2016</t>
+          <t>after 09/01/2016</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>2 unnamed round-3 participants</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Did not submit</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H48" s="3" t="n"/>
-      <c r="I48" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H48" s="2" t="n"/>
+      <c r="I48" s="2" t="n"/>
       <c r="J48" s="2" t="n"/>
       <c r="K48" s="2" t="n"/>
       <c r="L48" s="2" t="n"/>
       <c r="M48" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>Not stated</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O48" s="2" t="n"/>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>Inferred: Party C was a live rival when the target executed exclusivity with Insight (#45); no exit reported before this. Party C re-entered on 10/01 (#53).</t>
+          <t>Reported: on 09/01 the two other remaining participants were still considering and ultimately did not submit; date of decision not stated. Possibly includes Party A (see #34).</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Later on September 2, 2016, the parties signed an exclusivity agreement with an expiration time of 11:59 p.m. Eastern time on September 30, 2016. (p. 31)</t>
+          <t>“Both parties ultimately determined not to submit proposals” (p. 31)</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="S48" s="2" t="n"/>
       <c r="T48" s="4" t="n">
-        <v>42615</v>
-      </c>
-      <c r="U48" s="4" t="n"/>
-      <c r="V48" s="4" t="n">
-        <v>42615</v>
-      </c>
+        <v>42614</v>
+      </c>
+      <c r="U48" s="4" t="n">
+        <v>42614</v>
+      </c>
+      <c r="V48" s="2" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
@@ -3742,12 +3698,12 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>09/28/2016</t>
+          <t>09/01/2016</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3757,20 +3713,36 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H49" s="3" t="n"/>
-      <c r="I49" s="3" t="n"/>
-      <c r="J49" s="2" t="n"/>
-      <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
       <c r="M49" s="2" t="n">
         <v>1</v>
       </c>
@@ -3778,24 +3750,28 @@
       <c r="O49" s="2" t="n"/>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>New condition: Insight will not sign unless Datalink accepts its pro forma 8-K requests: adjustments completed and auditor consent obtained before closing (raised 09/23, drafted 09/26). Price stays $12.00.</t>
+          <t>Heavy: 30-day exclusivity still requested to sign; more diligence followed. Price raised from $11.75 to $12.00 after the target said its price was not competitive.</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>unless we would agree to Insight's requests that were discussed on September 23, 2016, and in subsequent drafts, Insight would not be willing to enter into the merger agreement (p. 32)</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="n"/>
+          <t>“On September 1, 2016, Insight increased its offer price to $12.00 per share.” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
       <c r="S49" s="2" t="n"/>
       <c r="T49" s="4" t="n">
-        <v>42641</v>
+        <v>42614</v>
       </c>
       <c r="U49" s="4" t="n">
-        <v>42641</v>
+        <v>42614</v>
       </c>
       <c r="V49" s="4" t="n">
-        <v>42641</v>
+        <v>42614</v>
       </c>
     </row>
     <row r="50">
@@ -3804,28 +3780,28 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>09/29/2016</t>
+          <t>09/01/2016</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
+          <t>Sullivan &amp; Cromwell LLP</t>
         </is>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Adviser</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H50" s="3" t="n"/>
-      <c r="I50" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="n"/>
       <c r="J50" s="2" t="n"/>
       <c r="K50" s="2" t="n"/>
       <c r="L50" s="2" t="n"/>
@@ -3834,24 +3810,24 @@
       <c r="O50" s="2" t="n"/>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>Board decision: let Insight's exclusivity lapse and approach Party B and Party C while still engaging Insight. Lidsky told Insight the board would not accept its requests but would talk further; Insight called them a requirement. Ref: $10.61 close 09/29/2016.</t>
+          <t>Insight's legal counsel; first shown acting 09/01/2016, negotiating Insight's proposed merger agreement with FaegreBD (termination fee cut from 4.0% to 3.5% of EV).</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>our board directed management to allow Insight's exclusivity period to expire and to approach Party B and Party C, while continuing to engage with Insight regarding Insight's requests (p. 32)</t>
+          <t>“FaegreBD contacted representatives of Sullivan &amp; Cromwell LLP, Insight's legal counsel, to discuss certain terms in Insight's proposed merger agreement” (p. 31)</t>
         </is>
       </c>
       <c r="R50" s="2" t="n"/>
       <c r="S50" s="2" t="n"/>
       <c r="T50" s="4" t="n">
-        <v>42642</v>
+        <v>42614</v>
       </c>
       <c r="U50" s="4" t="n">
-        <v>42642</v>
+        <v>42614</v>
       </c>
       <c r="V50" s="4" t="n">
-        <v>42642</v>
+        <v>42614</v>
       </c>
     </row>
     <row r="51">
@@ -3860,12 +3836,12 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>09/30/2016</t>
+          <t>09/02/2016</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3882,10 +3858,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H51" s="3" t="n"/>
-      <c r="I51" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H51" s="2" t="n"/>
+      <c r="I51" s="2" t="n"/>
       <c r="J51" s="2" t="n"/>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
@@ -3893,31 +3869,27 @@
         <v>1</v>
       </c>
       <c r="N51" s="2" t="n"/>
-      <c r="O51" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="O51" s="2" t="n"/>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>Ended (inferred): the board directed that exclusivity not be extended (#49). Raymond James re-contacted B and C on 10/01, and Insight later demanded a new exclusivity agreement.</t>
+          <t>Executed: 30-day exclusivity with Insight expiring 11:59 p.m. ET 09/30/2016, on board direction that day after it heard of the $12.00 and improved legal terms. Insight refused to shorten it to 20 days. Ref: $9.93 close.</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>the exclusivity period granted to Insight would expire on September 30, 2016 at 11:59 p.m. Eastern time if it was not extended (p. 32)</t>
+          <t>“Later on September 2, 2016, the parties signed an exclusivity agreement with an expiration time of 11:59 p.m. Eastern time on September 30, 2016” (p. 31)</t>
         </is>
       </c>
       <c r="R51" s="2" t="n"/>
       <c r="S51" s="2" t="n"/>
       <c r="T51" s="4" t="n">
-        <v>42643</v>
+        <v>42615</v>
       </c>
       <c r="U51" s="4" t="n">
-        <v>42643</v>
+        <v>42615</v>
       </c>
       <c r="V51" s="4" t="n">
-        <v>42643</v>
+        <v>42615</v>
       </c>
     </row>
     <row r="52">
@@ -3926,33 +3898,43 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>10/01/2016</t>
+          <t>by 09/02/2016</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Round opened</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" s="3" t="n"/>
-      <c r="I52" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H52" s="2" t="n"/>
+      <c r="I52" s="2" t="n"/>
       <c r="J52" s="2" t="n"/>
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
-      <c r="M52" s="2" t="n"/>
-      <c r="N52" s="2" t="n"/>
+      <c r="M52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Y</t>
@@ -3960,28 +3942,22 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>Unannounced round (inferred): after exclusivity lapsed, Raymond James re-contacted Party B and Party C and sent revised merger-agreement drafts answering their August mark-ups; negotiation with Insight continued. No due date. Inferred final (Q1).</t>
+          <t>Displaced when the target executed exclusivity with Insight (#50). The 09/01 board had found Party B's financing structure and third-party diligence requests problematic. Re-enters at #57.</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>Raymond James also sent Party B and Party C revised drafts of the merger agreement, reflecting comments from us to the drafts they provided on August 30 and 31, 2016 (p. 32)</t>
-        </is>
-      </c>
-      <c r="R52" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
+          <t>“Later on September 2, 2016, the parties signed an exclusivity agreement with an expiration time of 11:59 p.m. Eastern time on September 30, 2016” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="n"/>
       <c r="S52" s="2" t="n"/>
       <c r="T52" s="4" t="n">
-        <v>42644</v>
-      </c>
-      <c r="U52" s="4" t="n">
-        <v>42644</v>
-      </c>
+        <v>42615</v>
+      </c>
+      <c r="U52" s="2" t="n"/>
       <c r="V52" s="4" t="n">
-        <v>42644</v>
+        <v>42615</v>
       </c>
     </row>
     <row r="53">
@@ -3990,64 +3966,66 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>10/01/2016</t>
+          <t>by 09/02/2016</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H53" s="3" t="n"/>
-      <c r="I53" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="n"/>
       <c r="J53" s="2" t="n"/>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="n"/>
       <c r="M53" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N53" s="2" t="n"/>
-      <c r="O53" s="2" t="n"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>Party B, contacted by phone by Raymond James, expresses interest in re-engaging; it receives a revised draft merger agreement.</t>
+          <t>Displaced when the target executed exclusivity with Insight (#50). The 09/01 board had weighed Party C's price and financing arrangements. Re-enters at #58.</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>Raymond James contacted Party B and Party C by telephone, each of whom expressed interest on those calls in reengaging in the process. (p. 32)</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
+          <t>“Later on September 2, 2016, the parties signed an exclusivity agreement with an expiration time of 11:59 p.m. Eastern time on September 30, 2016” (p. 31)</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="n"/>
       <c r="S53" s="2" t="n"/>
       <c r="T53" s="4" t="n">
-        <v>42644</v>
-      </c>
-      <c r="U53" s="4" t="n">
-        <v>42644</v>
-      </c>
+        <v>42615</v>
+      </c>
+      <c r="U53" s="2" t="n"/>
       <c r="V53" s="4" t="n">
-        <v>42644</v>
+        <v>42615</v>
       </c>
     </row>
     <row r="54">
@@ -4056,32 +4034,32 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>10/01/2016</t>
+          <t>09/28/2016</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Re-entered</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H54" s="3" t="n"/>
-      <c r="I54" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H54" s="2" t="n"/>
+      <c r="I54" s="2" t="n"/>
       <c r="J54" s="2" t="n"/>
       <c r="K54" s="2" t="n"/>
       <c r="L54" s="2" t="n"/>
@@ -4092,28 +4070,28 @@
       <c r="O54" s="2" t="n"/>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>Party C, contacted by phone by Raymond James, expresses interest in re-engaging; it receives a revised draft merger agreement.</t>
+          <t>New requirement: Insight's 09/26 draft required pro forma 8-K adjustments to be done before closing and made auditor consent a closing condition (raised on a 09/23 call). On 09/28 Insight said it would not sign unless the target agreed. Price not restated.</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Raymond James contacted Party B and Party C by telephone, each of whom expressed interest on those calls in reengaging in the process. (p. 32)</t>
+          <t>“unless we would agree to Insight's requests that were discussed on September 23, 2016, and in subsequent drafts, Insight would not be willing to enter into the merger agreement” (p. 32)</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q5</t>
         </is>
       </c>
       <c r="S54" s="2" t="n"/>
       <c r="T54" s="4" t="n">
-        <v>42644</v>
+        <v>42641</v>
       </c>
       <c r="U54" s="4" t="n">
-        <v>42644</v>
+        <v>42641</v>
       </c>
       <c r="V54" s="4" t="n">
-        <v>42644</v>
+        <v>42641</v>
       </c>
     </row>
     <row r="55">
@@ -4122,19 +4100,15 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>10/03/2016</t>
+          <t>09/29/2016</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Party B</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -4144,38 +4118,36 @@
         <v>1</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H55" s="3" t="n"/>
-      <c r="I55" s="3" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="H55" s="2" t="n"/>
+      <c r="I55" s="2" t="n"/>
       <c r="J55" s="2" t="n"/>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M55" s="2" t="n"/>
       <c r="N55" s="2" t="n"/>
       <c r="O55" s="2" t="n"/>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>Constraint: Party B says it entered another transaction after its 08/30 proposal that must be completed before it can re-engage in full. No withdrawal at this point.</t>
+          <t>Board refused Insight's 8-K requests. It directed management to let Insight's exclusivity expire and approach Party B and Party C while still engaging Insight. The CEO told Insight, which replied that the requests were a requirement. Ref: $10.61 close.</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
         <is>
-          <t>they had entered into another transaction that would need to be completed before they would be able to re-engage in full on the proposed acquisition of the Company (p. 32)</t>
+          <t>“our board directed management to allow Insight's exclusivity period to expire and to approach Party B and Party C, while continuing to engage with Insight” (p. 32)</t>
         </is>
       </c>
       <c r="R55" s="2" t="n"/>
       <c r="S55" s="2" t="n"/>
       <c r="T55" s="4" t="n">
-        <v>42646</v>
+        <v>42642</v>
       </c>
       <c r="U55" s="4" t="n">
-        <v>42646</v>
+        <v>42642</v>
       </c>
       <c r="V55" s="4" t="n">
-        <v>42646</v>
+        <v>42642</v>
       </c>
     </row>
     <row r="56">
@@ -4184,80 +4156,64 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>10/04/2016</t>
+          <t>09/30/2016</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Financial</t>
+          <t>Strategic</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H56" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="I56" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>Heavy</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="H56" s="2" t="n"/>
+      <c r="I56" s="2" t="n"/>
+      <c r="J56" s="2" t="n"/>
+      <c r="K56" s="2" t="n"/>
+      <c r="L56" s="2" t="n"/>
       <c r="M56" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N56" s="2" t="n"/>
-      <c r="O56" s="2" t="n"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>Heavy: 30–45-day post-exclusivity signing period and absence of reported financing commitment carried from #40. Party C reaffirms $11.25 after re-engaging; recorded as its round-5 bid (Q2). Formal: its mark-up stands.</t>
+          <t>Ended: exclusivity lapsed unextended at 11:59 p.m. ET 09/30/2016. The lapse itself is not narrated; inferred from the 09/29 direction to let it expire and the 10/01 approach to Parties B and C. Insight stayed engaged.</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
         <is>
-          <t>On October 4, 2016, Party C reaffirmed its earlier offer of $11.25 per share. (p. 32)</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>Q2; Q7</t>
-        </is>
-      </c>
+          <t>“the exclusivity period granted to Insight would expire on September 30, 2016 at 11:59 p.m. Eastern time if it was not extended” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="n"/>
       <c r="S56" s="2" t="n"/>
       <c r="T56" s="4" t="n">
-        <v>42647</v>
+        <v>42643</v>
       </c>
       <c r="U56" s="4" t="n">
-        <v>42647</v>
+        <v>42643</v>
       </c>
       <c r="V56" s="4" t="n">
-        <v>42647</v>
+        <v>42643</v>
       </c>
     </row>
     <row r="57">
@@ -4266,60 +4222,62 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>10/06/2016</t>
+          <t>10/01/2016</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Exclusivity changed</t>
+          <t>Round opened</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H57" s="3" t="n"/>
-      <c r="I57" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="n"/>
       <c r="J57" s="2" t="n"/>
       <c r="K57" s="2" t="n"/>
       <c r="L57" s="2" t="n"/>
-      <c r="M57" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="M57" s="2" t="n"/>
       <c r="N57" s="2" t="n"/>
-      <c r="O57" s="2" t="n"/>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>Requested: Insight (Cowley) will do more work on the pro forma adjustments only with a revised draft and an exclusivity agreement. On 10/08 Sullivan &amp; Cromwell said Insight would not resume negotiations without its pro forma requests and new exclusivity.</t>
+          <t>Unannounced round, inferred from actions: after Insight's exclusivity lapsed, Raymond James re-contacted Parties B and C and sent them revised merger-agreement drafts responding to their 08/30-31 drafts. No due date. Live: Insight, Party B, Party C.</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
         <is>
-          <t>Insight would need to see a revised draft of the merger agreement and an exclusivity agreement (p. 32)</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="n"/>
+          <t>“On October 1, 2016, Raymond James contacted Party B and Party C by telephone, each of whom expressed interest on those calls in reengaging in the process” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S57" s="2" t="n"/>
       <c r="T57" s="4" t="n">
-        <v>42649</v>
+        <v>42644</v>
       </c>
       <c r="U57" s="4" t="n">
-        <v>42649</v>
+        <v>42644</v>
       </c>
       <c r="V57" s="4" t="n">
-        <v>42649</v>
+        <v>42644</v>
       </c>
     </row>
     <row r="58">
@@ -4328,54 +4286,64 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>10/13/2016</t>
+          <t>10/01/2016</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H58" s="3" t="n"/>
-      <c r="I58" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H58" s="2" t="n"/>
+      <c r="I58" s="2" t="n"/>
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="2" t="n"/>
       <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
+      <c r="M58" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="2" t="n"/>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>Target concedes: Lidsky tells Insight Datalink will proceed, grants further diligence access and accepts Insight's pro forma covenants. On 10/10 he had signalled exclusivity to 10/30 if open items were resolved.</t>
+          <t>Party B expressed interest in re-engaging when Raymond James called, and was sent a revised merger-agreement draft. Standing offer $12.00 (#44).</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
         <is>
-          <t>we were prepared to move forward with the proposed transaction and agreed to provide Insight with further access to due diligence, accepting Insight's proposed covenants (p. 33)</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="n"/>
+          <t>“Raymond James also sent Party B and Party C revised drafts of the merger agreement, reflecting comments from us to the drafts they provided on August 30 and 31” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S58" s="2" t="n"/>
       <c r="T58" s="4" t="n">
-        <v>42656</v>
+        <v>42644</v>
       </c>
       <c r="U58" s="4" t="n">
-        <v>42656</v>
+        <v>42644</v>
       </c>
       <c r="V58" s="4" t="n">
-        <v>42656</v>
+        <v>42644</v>
       </c>
     </row>
     <row r="59">
@@ -4384,54 +4352,64 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>10/20/2016</t>
+          <t>10/01/2016</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Re-entered</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H59" s="3" t="n"/>
-      <c r="I59" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="n"/>
       <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
-      <c r="M59" s="2" t="n"/>
+      <c r="M59" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N59" s="2" t="n"/>
       <c r="O59" s="2" t="n"/>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>Information access: draft Q3 financial statements and Q4 expectations posted for Insight and Party B only. Withheld from Party C because its $11.25 was below Insight's and Party B's $12.00 and it offered less certainty of closing.</t>
+          <t>Party C expressed interest in re-engaging when Raymond James called, and was sent a revised merger-agreement draft. Standing offer $11.25 (#45).</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
         <is>
-          <t>Party C was not provided this financial information because its re-affirmed proposed price of $11.25 per share was less than the price of $12.00 (p. 33)</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="n"/>
+          <t>“Raymond James also sent Party B and Party C revised drafts of the merger agreement, reflecting comments from us to the drafts they provided on August 30 and 31” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="4" t="n">
-        <v>42663</v>
+        <v>42644</v>
       </c>
       <c r="U59" s="4" t="n">
-        <v>42663</v>
+        <v>42644</v>
       </c>
       <c r="V59" s="4" t="n">
-        <v>42663</v>
+        <v>42644</v>
       </c>
     </row>
     <row r="60">
@@ -4440,7 +4418,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>10/24/2016</t>
+          <t>10/03/2016</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -4455,53 +4433,49 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Withdrew</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H60" s="3" t="n"/>
-      <c r="I60" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
       <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
       <c r="M60" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason</t>
-        </is>
-      </c>
+      <c r="N60" s="2" t="n"/>
       <c r="O60" s="2" t="n"/>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>Party B is 'not willing to acquire the Company at that time' and withdraws its $12.00 proposal (#39), citing among other things the draft Q3 statements. On 10/26 it was reported unwilling to proceed on its earlier terms (Q10).</t>
+          <t>Timing constraint: Party B said that, after its 08/30 proposal, it entered another transaction that had to close before it could fully re-engage. Not a withdrawal.</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
         <is>
-          <t>it was not willing to acquire the Company at that time and was withdrawing its earlier proposal, based on, among other things, our draft third quarter financial statements (p. 33)</t>
+          <t>“they had entered into another transaction that would need to be completed before they would be able to re-engage in full on the proposed acquisition of the Company” (p. 32)</t>
         </is>
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>Q10</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S60" s="2" t="n"/>
       <c r="T60" s="4" t="n">
-        <v>42667</v>
+        <v>42646</v>
       </c>
       <c r="U60" s="4" t="n">
-        <v>42667</v>
+        <v>42646</v>
       </c>
       <c r="V60" s="4" t="n">
-        <v>42667</v>
+        <v>42646</v>
       </c>
     </row>
     <row r="61">
@@ -4510,15 +4484,19 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>10/24/2016</t>
+          <t>10/04/2016</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="n"/>
+          <t>Party C</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Financial</t>
+        </is>
+      </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Other material event</t>
@@ -4528,36 +4506,42 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H61" s="3" t="n"/>
-      <c r="I61" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H61" s="2" t="n"/>
+      <c r="I61" s="2" t="n"/>
       <c r="J61" s="2" t="n"/>
       <c r="K61" s="2" t="n"/>
       <c r="L61" s="2" t="n"/>
-      <c r="M61" s="2" t="n"/>
+      <c r="M61" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N61" s="2" t="n"/>
       <c r="O61" s="2" t="n"/>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>Information access: draft Q3 GAAP financial statements provided to Insight only. Party B withdrew the same day; Party C had been excluded from Q3 information (#58).</t>
+          <t>Reaffirmation: Party C reaffirmed its earlier $11.25 offer (#45), terms unchanged. Recorded here rather than as a Bid or Bid reaffirmed because nothing changed and the target was not finalizing with Party C (E10).</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
         <is>
-          <t>On October 24, 2016, we provided to Insight a draft of our third quarter GAAP financial statements. (p. 33)</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="n"/>
+          <t>“On October 4, 2016, Party C reaffirmed its earlier offer of $11.25 per share.” (p. 32)</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q7</t>
+        </is>
+      </c>
       <c r="S61" s="2" t="n"/>
       <c r="T61" s="4" t="n">
-        <v>42667</v>
+        <v>42647</v>
       </c>
       <c r="U61" s="4" t="n">
-        <v>42667</v>
+        <v>42647</v>
       </c>
       <c r="V61" s="4" t="n">
-        <v>42667</v>
+        <v>42647</v>
       </c>
     </row>
     <row r="62">
@@ -4566,12 +4550,12 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>10/26/2016</t>
+          <t>10/06/2016</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4588,10 +4572,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H62" s="3" t="n"/>
-      <c r="I62" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H62" s="2" t="n"/>
+      <c r="I62" s="2" t="n"/>
       <c r="J62" s="2" t="n"/>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
@@ -4602,28 +4586,28 @@
       <c r="O62" s="2" t="n"/>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>Executed after the board meeting: Insight (Lamneck) confirms its $12.00 offer, and exclusivity runs to 9:00 a.m. 11/07/2016 for diligence and negotiation. Datalink had deferred Insight's 10/20 demand until this meeting. No Bid reaffirmed row: #44 is Formal, in a final round (Q2). Ref: $10.03 close.</t>
+          <t>Requested: after the CEO re-contacted Insight on 10/04, Insight said further 8-K work needed a revised draft and an exclusivity agreement. On 10/08 its counsel said talks would not resume without the 8-K terms and new exclusivity.</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
         <is>
-          <t>we executed the exclusivity agreement with Insight granting Insight exclusivity through 9:00 a.m. on November 7, 2016 (p. 33)</t>
+          <t>“Insight would need to see a revised draft of the merger agreement and an exclusivity agreement” (p. 32)</t>
         </is>
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S62" s="2" t="n"/>
       <c r="T62" s="4" t="n">
-        <v>42669</v>
+        <v>42649</v>
       </c>
       <c r="U62" s="4" t="n">
-        <v>42669</v>
+        <v>42649</v>
       </c>
       <c r="V62" s="4" t="n">
-        <v>42669</v>
+        <v>42649</v>
       </c>
     </row>
     <row r="63">
@@ -4632,70 +4616,58 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>by 10/26/2016</t>
+          <t>10/13/2016</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Party C</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Financial</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Dropped by target</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H63" s="3" t="n"/>
-      <c r="I63" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H63" s="2" t="n"/>
+      <c r="I63" s="2" t="n"/>
       <c r="J63" s="2" t="n"/>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="M63" s="2" t="n"/>
+      <c r="N63" s="2" t="n"/>
+      <c r="O63" s="2" t="n"/>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>Inferred: Party C was a live rival when exclusivity was executed with Insight (#61); its last bid is #55. The 10/26 board weighed its lower price and closing certainty. On 11/02 the board still mentioned 'other interested parties' (Q9).</t>
+          <t>Target moved to finalize with Insight: it accepted Insight's pro forma covenants, said it was ready to proceed, and gave Insight further diligence access. On 10/10 the CEO signalled exclusivity to 10/30 if open items were resolved. Exclusivity deferred on 10/20 to after the 10/26 board.</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
         <is>
-          <t>Our board discussed Party C's lower proposed price of $11.25 per share and the greater certainty of closing offered by the Insight proposal. (p. 33)</t>
+          <t>“agreed to provide Insight with further access to due diligence, accepting Insight's proposed covenants regarding the pro forma combined financial statements” (p. 33)</t>
         </is>
       </c>
       <c r="R63" s="2" t="inlineStr">
         <is>
-          <t>Q9</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S63" s="2" t="n"/>
       <c r="T63" s="4" t="n">
-        <v>42669</v>
-      </c>
-      <c r="U63" s="4" t="n"/>
+        <v>42656</v>
+      </c>
+      <c r="U63" s="4" t="n">
+        <v>42656</v>
+      </c>
       <c r="V63" s="4" t="n">
-        <v>42669</v>
+        <v>42656</v>
       </c>
     </row>
     <row r="64">
@@ -4704,80 +4676,58 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>11/01/2016</t>
+          <t>10/20/2016</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Strategic</t>
-        </is>
-      </c>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Other material event</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>Not stated</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="n"/>
       <c r="O64" s="2" t="n"/>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>Light: no financing needed; remaining diligence completed 11/02–11/06. Price cut from $12.00 (#44) after a detailed review of Q3 results and Q4 expectations, requested 10/28, citing gross-margin erosion. Formal: agreement being finalized.</t>
+          <t>Information access: draft Q3 statements and Q4 expectations went to the data room for Insight and Party B, not Party C (its $11.25 trailed $12.00 and its closing was less certain). Insight alone got draft Q3 GAAP statements on 10/24. The Projections went to Insight (p. 39).</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
         <is>
-          <t>Insight was reducing its offer price to $11.00 per share (p. 34)</t>
+          <t>“Party C was not provided this financial information because its re-affirmed proposed price of $11.25 per share was less than the price of $12.00” (p. 33)</t>
         </is>
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q1</t>
         </is>
       </c>
       <c r="S64" s="2" t="n"/>
       <c r="T64" s="4" t="n">
-        <v>42675</v>
+        <v>42663</v>
       </c>
       <c r="U64" s="4" t="n">
-        <v>42675</v>
+        <v>42663</v>
       </c>
       <c r="V64" s="4" t="n">
-        <v>42675</v>
+        <v>42663</v>
       </c>
     </row>
     <row r="65">
@@ -4786,54 +4736,68 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>11/02/2016</t>
+          <t>10/24/2016</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Datalink</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="n"/>
+          <t>Party B</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Other material event</t>
+          <t>Withdrew</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H65" s="3" t="n"/>
-      <c r="I65" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
       <c r="J65" s="2" t="n"/>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
-      <c r="M65" s="2" t="n"/>
-      <c r="N65" s="2" t="n"/>
+      <c r="M65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>Value below earlier offer</t>
+        </is>
+      </c>
       <c r="O65" s="2" t="n"/>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>Counter-proposal: after a call with Raymond James and board chair Ousley, Lidsky asks Insight to raise its revised price to $11.25.</t>
+          <t>Party B said it was not willing to acquire the Company 'at that time' and withdrew its $12.00 proposal (#44), citing among other things the draft Q3 statements. The board heard it was no longer willing on the terms of its earlier proposal (p. 33).</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>Mr. Lidsky contacted Mr. Lamneck and requested that Insight increase its revised offer price to $11.25 per share. (p. 34)</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="n"/>
+          <t>“Party B indicated that it was not willing to acquire the Company at that time and was withdrawing its earlier proposal” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q8</t>
+        </is>
+      </c>
       <c r="S65" s="2" t="n"/>
       <c r="T65" s="4" t="n">
-        <v>42676</v>
+        <v>42667</v>
       </c>
       <c r="U65" s="4" t="n">
-        <v>42676</v>
+        <v>42667</v>
       </c>
       <c r="V65" s="4" t="n">
-        <v>42676</v>
+        <v>42667</v>
       </c>
     </row>
     <row r="66">
@@ -4842,12 +4806,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>11/02/2016</t>
+          <t>10/26/2016</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Insight Enterprises, Inc.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4857,36 +4821,20 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Bid</t>
+          <t>Exclusivity changed</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Formal</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>Light</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="H66" s="2" t="n"/>
+      <c r="I66" s="2" t="n"/>
+      <c r="J66" s="2" t="n"/>
+      <c r="K66" s="2" t="n"/>
+      <c r="L66" s="2" t="n"/>
       <c r="M66" s="2" t="n">
         <v>1</v>
       </c>
@@ -4894,28 +4842,28 @@
       <c r="O66" s="2" t="n"/>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>Light: no financing needed; diligence and documentation completed 11/02–11/06. Insight accepts the $11.25 counter on a later call, and the board directs the deal to be finalized at $11.25. Cash: this is the signed $11.25 cash consideration. Ref: $9.35 close 11/02/2016.</t>
+          <t>Executed: exclusivity through 9:00 a.m. 11/07/2016. The board weighed Party C's lower $11.25 and Insight's greater closing certainty. Before signing, Insight confirmed its offer including $12.00 (carried from #48; no Bid reaffirmed row, E10). Ref: $10.03 close.</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
         <is>
-          <t>On a subsequent call, Mr. Lamneck agreed to the increased offer price of $11.25 per share. (p. 34)</t>
+          <t>“we executed the exclusivity agreement with Insight granting Insight exclusivity through 9:00 a.m. on November 7, 2016” (p. 33)</t>
         </is>
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>Q7</t>
+          <t>Q1; Q7</t>
         </is>
       </c>
       <c r="S66" s="2" t="n"/>
       <c r="T66" s="4" t="n">
-        <v>42676</v>
+        <v>42669</v>
       </c>
       <c r="U66" s="4" t="n">
-        <v>42676</v>
+        <v>42669</v>
       </c>
       <c r="V66" s="4" t="n">
-        <v>42676</v>
+        <v>42669</v>
       </c>
     </row>
     <row r="67">
@@ -4924,60 +4872,70 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>11/06/2016</t>
+          <t>by 10/26/2016</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Insight</t>
+          <t>Party C</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Strategic</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Merger agreement signed</t>
+          <t>Dropped by target</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
         <v>1</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H67" s="3" t="n"/>
-      <c r="I67" s="3" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="H67" s="2" t="n"/>
+      <c r="I67" s="2" t="n"/>
       <c r="J67" s="2" t="n"/>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>$11.25 per share in cash, via Reef Acquisition Co. Directors' voting agreement (about 7.0% of shares) signed at the same time. Termination fee $7.5 million; no financing condition. Raymond James fairness opinion delivered 11/06. Premium 19.3% over 11/04 close.</t>
+          <t>Displaced when the target executed exclusivity with Insight (#65). The board had weighed Party C's lower $11.25 price and lower closing certainty; not reported contacted again.</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
         <is>
-          <t>The parties executed the merger agreement during the evening of Sunday, November 6, 2016 (p. 35)</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="n"/>
+          <t>“to enter into an exclusivity agreement with Insight for an exclusivity period ending November 7, 2016” (p. 33)</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
       <c r="S67" s="2" t="n"/>
       <c r="T67" s="4" t="n">
-        <v>42680</v>
-      </c>
-      <c r="U67" s="4" t="n">
-        <v>42680</v>
-      </c>
+        <v>42669</v>
+      </c>
+      <c r="U67" s="2" t="n"/>
       <c r="V67" s="4" t="n">
-        <v>42680</v>
+        <v>42669</v>
       </c>
     </row>
     <row r="68">
@@ -4986,60 +4944,350 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>11/07/2016</t>
+          <t>11/01/2016</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Datalink and Insight</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="n"/>
+          <t>Insight Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Merger announced</t>
+          <t>Bid</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>post</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="n"/>
+      <c r="G68" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>1</v>
+      </c>
       <c r="N68" s="2" t="n"/>
       <c r="O68" s="2" t="n"/>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>Joint press release issued before market open on Monday 11/07/2016.</t>
+          <t>Heavy: required pre-closing 8-K work and auditor-consent closing condition (#53) stood; commercial and legal diligence still open. Price cut from $12.00 citing Q3 results, including gross margin erosion, after a detailed financial review requested on 10/28.</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
         <is>
-          <t>Insight and we issued a joint press release prior to the opening of the market on Monday, November 7, 2016, announcing the parties' entry into the merger agreement (p. 35)</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="n"/>
+          <t>“based on the third quarter financial results, including the gross margin erosion in the third quarter, and additional information provided, Insight was reducing its offer price to $11.00 per share” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q5</t>
+        </is>
+      </c>
       <c r="S68" s="2" t="n"/>
       <c r="T68" s="4" t="n">
+        <v>42675</v>
+      </c>
+      <c r="U68" s="4" t="n">
+        <v>42675</v>
+      </c>
+      <c r="V68" s="4" t="n">
+        <v>42675</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>11/02/2016</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Datalink</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Other material event</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>Counter-proposal: after a call with Raymond James and chair Ousley, the CEO asked Insight to raise its revised price from $11.00 to $11.25.</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>“Mr. Lidsky contacted Mr. Lamneck and requested that Insight increase its revised offer price to $11.25 per share” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="n"/>
+      <c r="T69" s="4" t="n">
+        <v>42676</v>
+      </c>
+      <c r="U69" s="4" t="n">
+        <v>42676</v>
+      </c>
+      <c r="V69" s="4" t="n">
+        <v>42676</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>11/02/2016</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Insight Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Bid</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>Not stated</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Heavy</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N70" s="2" t="n"/>
+      <c r="O70" s="2" t="n"/>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>Heavy: same auditor-consent condition; diligence completed only 11/02-11/06. Accepted the target's $11.25 counter on a later call. The board then directed finalizing at $11.25, believing further talks would not yield a superior proposal. Ref: $9.35 close.</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>“On a subsequent call, Mr. Lamneck agreed to the increased offer price of $11.25 per share.” (p. 34)</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr">
+        <is>
+          <t>Q1; Q5</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="n"/>
+      <c r="T70" s="4" t="n">
+        <v>42676</v>
+      </c>
+      <c r="U70" s="4" t="n">
+        <v>42676</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>42676</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>11/06/2016</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Insight Enterprises, Inc.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Strategic</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Merger agreement signed</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>Agreed: $11.25 per share in cash via Reef Acquisition Co.; board unanimous after Raymond James fairness opinion; directors' voting agreements; $7.5m termination fee; no financing condition; auditor-consent closing condition. Signed Sunday evening.</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>“The parties executed the merger agreement during the evening of Sunday, November 6, 2016” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="n"/>
+      <c r="T71" s="4" t="n">
+        <v>42680</v>
+      </c>
+      <c r="U71" s="4" t="n">
+        <v>42680</v>
+      </c>
+      <c r="V71" s="4" t="n">
+        <v>42680</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>11/07/2016</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Datalink and Insight</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Merger announced</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>post</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>Joint press release before market open on Monday 11/07/2016. Price $11.25 was a 19.3% premium to the 11/04/2016 close (p. 37).</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>“Insight and we issued a joint press release prior to the opening of the market on Monday, November 7, 2016” (p. 35)</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="n"/>
+      <c r="S72" s="2" t="n"/>
+      <c r="T72" s="4" t="n">
         <v>42681</v>
       </c>
-      <c r="U68" s="4" t="n">
+      <c r="U72" s="4" t="n">
         <v>42681</v>
       </c>
-      <c r="V68" s="4" t="n">
+      <c r="V72" s="4" t="n">
         <v>42681</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V68"/>
+  <autoFilter ref="A1:V72"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5050,19 +5298,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5125,26 +5373,26 @@
         <v>1</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>42398</v>
+        <v>42527</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Board decides to pursue Party A's unsolicited approach (bilateral; inferred)</t>
+          <t>Raymond James outreach: 13 strategic acquirers from 06/06/2016, 14 financial sponsors later in June (#13).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>1 strategic: Party A</t>
+          <t>23 NDA signers: 10 Strategic (Party A, which carried over from round 0, Party B, Insight, 7 unnamed) and 13 Financial (Party C, 12 unnamed).</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>none stated</t>
+          <t>07/18/2016 (strategic buyers); 07/21/2016 (financial sponsors)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>No deadline stated</t>
+          <t>Enforced; Enforced</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -5154,12 +5402,12 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>1: Party A (03/29 proposal; updated 04/12)</t>
+          <t>10: 9 new IOIs (4 Strategic incl. Insight, Party B; 5 Financial incl. Party C) plus Party A's standing 03/29 proposal, counted by the board.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Board declined to pursue 'at that time' (04/20) but kept Party A in view; Party A carried into round 2 outreach</t>
+          <t>Five advanced (Insight, Party B, Party C, 2 unnamed, possibly incl. Party A); five IOI holders dropped; 13 NDA signers did not submit (5 Strategic, 8 Financial).</t>
         </is>
       </c>
     </row>
@@ -5171,26 +5419,26 @@
         <v>2</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>42527</v>
+        <v>42578</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Raymond James begins outreach: 13 strategic, then 14 financial sponsors</t>
+          <t>Board selected the five highest-priced IOI holders; management presentations and more diligence followed (#35).</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>23 NDA signers: 10 strategic (Party A, Party B, Insight, 7 unnamed); 13 financial (Party C, 12 unnamed)</t>
+          <t>5: Insight (Strategic), Party B (Strategic), Party C (Financial), 2 unnamed (type unknown; possibly incl. Party A).</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>07/18/2016 (strategic buyers); 07/21/2016 (financial sponsors) – parallel due dates</t>
+          <t>none stated</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Enforced; Enforced</t>
+          <t>No deadline stated</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -5200,12 +5448,12 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>10: Insight, Party B, Party C, 6 unnamed (2 strategic, 4 financial); Party A's 03/29 proposal counted as its IOI</t>
+          <t>0: no offers requested in this stage.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>five advanced, five not selected, thirteen did not submit</t>
+          <t>All five carried into the final round by the 08/16 instruction letters.</t>
         </is>
       </c>
     </row>
@@ -5217,41 +5465,41 @@
         <v>3</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>42578</v>
+        <v>42598</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Board advances the five highest-priced IOIs to a second diligence stage</t>
+          <t>Instruction letters for final proposals with merger-agreement mark-up (#37); later called 'best and final' (p. 36).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5: Insight, Party B (strategic); Party C (financial); 2 unnamed (type not stated; could include Party A)</t>
+          <t>5: Insight (Strategic), Party B (Strategic), Party C (Financial) (letters reported); 2 unnamed that remained in the process (letters not reported).</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>none stated</t>
+          <t>08/30/2016 5:00 p.m. ET</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>No deadline stated</t>
+          <t>Late bids accepted</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Not final</t>
+          <t>Announced as final</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3: Party B and Party C on 08/30, Insight on 08/31 (late), with revisions to 09/01 (Insight to $12.00, Party C to $11.25).</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Final-proposal letters sent to Insight, Party B and Party C; the two unnamed remained in process</t>
+          <t>Exclusivity with Insight 09/02; Parties B and C dropped; 2 unnamed did not submit. Exclusivity lapsed 09/30 unextended.</t>
         </is>
       </c>
     </row>
@@ -5263,92 +5511,46 @@
         <v>4</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>42598</v>
+        <v>42644</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Final-proposal instruction letters with mark-up requirement</t>
+          <t>Inferred: after Insight's exclusivity lapsed, Raymond James re-contacted Parties B and C and sent revised merger-agreement drafts (#56).</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3 invited: Insight, Party B (strategic), Party C (financial); 2 unnamed advancers remaining in process, letter not reported</t>
+          <t>3: Insight (Strategic, carried over), Party B (Strategic, re-entered), Party C (Financial, re-entered).</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>08/30/2016 5:00 p.m. ET</t>
+          <t>none stated</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted</t>
+          <t>No deadline stated</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Announced as final</t>
+          <t>Inferred final</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3: Party B, Party C (08/30), Insight (08/31); revisions by all three; Insight to $12.00 on 09/01</t>
+          <t>1: Insight ($11.00 on 11/01, $11.25 on 11/02). Party C reaffirmed $11.25 (#60) and Insight confirmed $12.00 (#65), neither recorded as a bid.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>Insight selected; exclusivity 09/02; Party B and Party C out at exclusivity (inferred); two unnamed did not submit</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>42644</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>After Insight's exclusivity lapsed, Party B and Party C re-contacted with revised drafts (inferred round)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3: Insight, Party B (strategic); Party C (financial)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>none stated</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>No deadline stated</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Inferred final</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2: Party C (reaffirmed $11.25 on 10/04); Insight ($11.00 on 11/01, $11.25 on 11/02)</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>signing with Insight 11/06; Party B withdrew 10/24; Party C out at 10/26 exclusivity (inferred)</t>
+          <t>Signing with Insight 11/06/2016 at $11.25; Party B withdrew 10/24; Party C dropped at 10/26 exclusivity.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J6"/>
+  <autoFilter ref="A1:J5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5359,15 +5561,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -5416,27 +5618,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Is the map right? One process. Round 0: Party A's 01/19 approach. Round 1: bilateral stage with Party A (01/29). Round 2: broad outreach (06/06). Round 3: five-party second stage (07/27). Round 4: final proposals (08/16). Round 5: re-engagement after exclusivity lapsed (10/01).</t>
+          <t>Is the map right: one process; Party A's January-May 2016 dealings as round 0; round 1 = 06/06 outreach, round 2 = 07/27 selection of five, round 3 = 08/16 final-proposal letters, round 4 = 10/01 re-approach of Parties B and C after Insight's exclusivity lapsed?</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Keep this map. Alternatives: (i) all pre-June Party A activity in round 0, with outreach as round 1; (ii) merge rounds 3 and 4, making the 08/16 letter a Deadline set; (iii) no round 5, with October treated as a continuation of round 4.</t>
+          <t>Keep as drafted: one process, rounds 0 and 1-4, signing in round 4 and the announcement post.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>E5 tests for a second process: (a) not met, since Party A was kept in view after 04/20 (talks through May; on the June list, p.27–28); (b) not met, with no reported end and no gap of 2+ months without acquirer contact; (c) met by the 05/25 and 06/01 decisions, but moot. Round 1 is solicited: the target requested Party A's written proposal (p.27). Raymond James re-invited Party B and Party C on 10/01 (p.32).</t>
+          <t>E5: (a) not met, since Party A was kept in view (talks Feb-May, p. 27; named for outreach, p. 28); (b) not met, no gap of about two months or more without acquirer contact (longest: 04/20 to 06/06, with undated May talks); (c) met on 05/25 and 06/01 (p. 28). Round 1 = first outreach wave (E6). Round 3 = first final request (p. 29). Round 4 inferred from 10/01 re-invitation (p. 32).</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>#5, #7, #8, #9, #10, #11, #14, #29, #32, #51</t>
+          <t>#7, #8, #9, #10, #11, #12, #13, #35, #37, #56, #57, #58, #59, #60, #61, #62, #63, #64, #65, #66, #67, #68, #69, #70</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>(i) Rows for Party A move to round 0, and rounds renumber 1–4. (ii) Round 3 vanishes, and the five advancers face the final solicitation. (iii) B and C's October status joins round 4, and Round 5's line disappears.</t>
+          <t>Most plausible alternative: no round 4, so the October re-approach continues round 3 (#56 deleted; #57-#70 move to round 3). Less plausible: the mid-March request (#7) opens a bilateral round 1 for Party A (#7-#12, then renumber); or rounds 2 and 3 merge (#35, #37).</t>
         </is>
       </c>
       <c r="G2" s="2" t="n"/>
@@ -5449,27 +5651,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>How should reaffirmations be treated? Party A's 04/12 and Party C's 10/04 are recorded as Bid rows; Insight's 10/26 price confirmation gets no Bid reaffirmed row.</t>
+          <t>How should Party A be carried through the June process, given the filing counts its 03/29 proposal alongside the new IOIs but never says whether it was among the five advanced?</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Keep as recorded.</t>
+          <t>As drafted: Party A counts as a round-1 IOI holder. Its exit stays inside the uncertain residual: the 5 dropped at 07/27 (#34) or the 2 unnamed advancers who did not submit (#47). The 04/12 updated IOI stays a separate Bid.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>E10 allows Bid reaffirmed only once the target is finalizing with that bidder, which was not the case for A or C. Party A's was an 'updated indication of interest' affirming 'substantially all' terms (p.27). Party C's is its only round-5 response (p.32). Insight's latest row (09/01) is already Formal and in final round 4.</t>
+          <t>p. 29 lists four strategic IOIs 'in addition to Party A', and the $8.80-$10.50 'other' range may or may not include Party A's $10.30 floor. p. 29-31 name only Insight, B and C among the five. E14 keeps a party of uncertain membership inside the residual.</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>#10, #55, #61</t>
+          <t>#9, #29, #30, #34, #35, #47</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Dropping those rows leaves round 5 with Insight's bids only, and Party C's last bid in round 4. Adding Insight's 10/26 confirmation adds a $12.00 row in round 5.</t>
+          <t>If Party A is not an IOI holder: #29 becomes 6, IOI holders 9 and #34 becomes 4. If Party A was among the five, its exit is round-3 Did not submit. Folding #9 into #8 removes one Party A bid.</t>
         </is>
       </c>
       <c r="G3" s="2" t="n"/>
@@ -5482,27 +5684,27 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Where is Party A after July? Did it sign a new NDA in June, and was it among the five advanced on 07/27?</t>
+          <t>Round 1 deadline outcomes for the 07/18/2016 (strategic) and 07/21/2016 (financial) IOI due dates.</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>No new entry for Party A in June. Leave its later status inside the cohorts: the not-selected five (#30) or the two unnamed advancers (#42).</t>
+          <t>Enforced; Enforced.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>p.28 counts Party A among the 10 strategic NDA signers, but its NDA dates from 02/04 (p.27). Its $10.30–$10.75 proposal was counted among the IOIs, and its top exceeds the others' $10.50 maximum (p.29). Yet the filing names Party B and Party C and not Party A among the five.</t>
+          <t>On 07/27 the board reviewed the IOIs received and advanced five on them (p. 29). No extension, and no IOI arriving after a due date, is reported. The communication setting the dates is undated (p. 29).</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>#16, #30, #42</t>
+          <t>#25, #28, #32</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>If Party A advanced, it becomes one of the two did-not-submit parties in round 4, and the not-selected cohort is all unnamed parties. Its exit then says less about a low valuation.</t>
+          <t>If the arrival days (not reported) are read as unknown, both become Unclear. That changes only the Rounds outcome for round 1, not bids or exits.</t>
         </is>
       </c>
       <c r="G4" s="2" t="n"/>
@@ -5515,27 +5717,27 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Round 2 deadline outcomes: were the 07/18 (strategic) and 07/21 (financial) IOI due dates enforced?</t>
+          <t>Are the round-1 exits labelled correctly: NDA signers without IOIs as inferred Did not submit, and the five non-advanced IOI holders as Dropped by target for 'Lower offer than rivals'?</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Enforced; Enforced.</t>
+          <t>Keep both as drafted.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>The board reviewed the IOIs received and advanced five on 07/27; no late or extended submissions are reported (p.29). Party A's 03/29 proposal was counted as its IOI without a new submission (p.29).</t>
+          <t>Raymond James told 'the interested parties' the IOI due dates (p. 29), which I read as all NDA signers in data rooms. The board kept 'the five parties that submitted the highest-priced initial indications' (p. 29), which states why the rest were not advanced.</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>#19, #23, #27</t>
+          <t>#29, #33, #34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Unclear instead, if one treats the lack of arrival dates as leaving open whether any IOI came after its due date.</t>
+          <t>If the due-date notice reached only some signers, the others become Dropped by target by 07/27 (#29, #33). If inferred exits keep the default reason, #34 becomes Not stated and loses its valuation signal.</t>
         </is>
       </c>
       <c r="G5" s="2" t="n"/>
@@ -5548,27 +5750,27 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Are the did-not-submit counts exact (5 strategic, 8 financial)? They assume every IOI submitter was an NDA signer.</t>
+          <t>Are the Conditions right in rating every Formal bid Heavy, and in treating Insight's 09/28 pre-closing 8-K and auditor-consent demand as an Other material event rather than a new Bid?</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Keep 5 and 8 as exact, marked Inferred.</t>
+          <t>Keep Heavy throughout, and keep #53 as an Other material event.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>IOIs were requested from 'the interested parties', and NDA signers were given the data room (p.28–29). p.36: 27 contacted, 23 NDAs. The filing never says expressly that each unnamed submitter had signed an NDA.</t>
+          <t>Each 08/30-09/01 bid sought a 30-day or 30-45 day exclusive period to reach a definitive agreement (p. 29-31), with B's financing and reverse termination fee and C's uncommitted financing on top. Insight's 11/01-11/02 bids carried its required auditor-consent closing condition (p. 32), a completion risk per p. 38, with diligence open until 11/02-11/06 (p. 34).</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>#24, #26, #28</t>
+          <t>#38, #39, #41, #43, #44, #45, #48, #53, #67, #69</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Counts become ranges: strategic 5–7, since the 3 non-signers could include the 2 unnamed strategic submitters, and financial 8–9. Count cells go blank.</t>
+          <t>Reading the exclusivity periods as documentation time makes Insight's 08/31-09/01 bids Light. Reading Insight's 11/01-11/02 bids as unconditioned but with diligence open makes them Unclear. Either weakens any later reinterpretation of them as informal.</t>
         </is>
       </c>
       <c r="G6" s="2" t="n"/>
@@ -5581,27 +5783,27 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Were the two unnamed advancers part of round 4, given that the final-proposal letter and draft merger agreement went only to Insight, Party B and Party C?</t>
+          <t>Round 3 deadline outcome for the 5:00 p.m. ET 08/30/2016 final-proposal due date.</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Yes: list them as 'remaining, letter not reported', with the reported Did not submit exit.</t>
+          <t>Late bids accepted.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>On 09/01 Raymond James said two of the five 'had not submitted proposals' and 'remained in the process', still considering whether to submit; both 'ultimately determined not to submit' (p.30–31).</t>
+          <t>The letter set 5:00 p.m. ET on 08/30 (p. 29). Parties B and C submitted on 08/30, Insight on 08/31 (p. 29). Insight's bid was reviewed that day, improved, and led to exclusivity (p. 30-31). No extension is reported.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>#31, #32, #42</t>
+          <t>#40, #41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Otherwise they were Dropped by target on 08/16 (not invited), in round 3, and round 4's set is exactly three.</t>
+          <t>If Insight had been given more time informally (not reported), the outcome would be Extended or Passed without action. Only the Rounds outcome changes.</t>
         </is>
       </c>
       <c r="G7" s="2" t="n"/>
@@ -5614,27 +5816,27 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Conditions on final-stage bids: all Heavy until Insight's November bids (Light)?</t>
+          <t>Should Party C's 10/04 reaffirmation of $11.25 and Insight's 10/26 confirmation of $12.00 be Bid or Bid reaffirmed rows in round 4?</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Keep. Each final-round bid tied signing to a stated 30-day (Party C: 30–45-day) exclusive period, which E12 counts as Heavy. Insight's November bids needed no financing, and its diligence finished within days.</t>
+          <t>No. Keep #60 as an Other material event and Insight's confirmation in the Note of #65.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>p.29–30 give the 30-day and 30–45-day periods, Party B's debt financing with a reverse termination fee, and Party C's financing that was 'still exploring'. p.34 has Insight completing diligence 11/02–11/06; p.48 says no financing condition.</t>
+          <t>E10 records Bid reaffirmed only where the latest priced row is Informal or sits in a Not-final round. #45 and #48 are Formal and sit in round 3, announced as final (p. 29, 36). Party C's terms did not change, and the target was not finalizing with Party C (p. 32-33).</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>#33, #34, #36, #38, #39, #40, #44, #55, #63, #65</t>
+          <t>#60, #65</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Light for Insight's 09/01 $12.00 bid (no financing needed, employment condition dropped) would make it the only near-unconditional formal bid before exclusivity.</t>
+          <t>As bid rows, round 4 would show priced submissions from Party C ($11.25, Formal, Heavy) and from Insight ($12.00 before its 11/01 cut), and Bids received for round 4 would rise from 1 to 2.</t>
         </is>
       </c>
       <c r="G8" s="2" t="n"/>
@@ -5647,99 +5849,33 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Round 4 deadline outcome: 08/30/2016, 5:00 p.m. ET. Insight's proposal arrived on 08/31.</t>
+          <t>Party B's exit reason on 10/24: Value below earlier offer, or Other stated reason?</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Late bids accepted.</t>
+          <t>Value below earlier offer.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Party B and Party C submitted on 08/30; Insight submitted on 08/31. Its proposal was reviewed that day and considered, and later preferred, at the 09/01 board (p.29–31). No extension is reported.</t>
+          <t>Party B withdrew 'based on, among other things, our draft third quarter financial statements', and the board heard it was 'no longer willing to acquire us on the terms set forth in its earlier proposal' (p. 33). So its value fell below its $12.00 offer.</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>#35, #36</t>
+          <t>#64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Enforced, if Insight's timing had been agreed in advance; that is not reported.</t>
+          <t>Other stated reason would reflect its timing constraints: 'at that time' (p. 33) and its other pending transaction (p. 32). The model then gets no valuation signal from Party B's exit.</t>
         </is>
       </c>
       <c r="G9" s="2" t="n"/>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Q9</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Should Party B and Party C be treated as dropped at Insight's 09/02 exclusivity and re-entered on 10/01, and Party C dropped again at the 10/26 exclusivity?</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Keep, per the E14 exclusivity rule.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Exclusivity was executed on 09/02 and 10/26 (p.31, 33). The board kept B and C in reserve: on 09/29 it would be 'free to contact' them (p.32), and on 11/02 it referred to 'the other interested parties' (p.34).</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>#46, #47, #52, #53, #62</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>If kept live: no Sept drop or re-entry rows; three live bidders throughout; Party C Not selected at signing on 11/06.</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Q10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Party B's exit reason: Other stated reason, or Value below earlier offer?</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Other stated reason.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Party B was unwilling 'at that time', citing the draft Q3 statements 'among other things' (p.33); it also had a pending other transaction (p.32). The board was told it would not proceed 'on the terms set forth in its earlier proposal' (p.33).</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>#59</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Value below earlier offer would record that B's valuation, after seeing Q3, fell below $12.00.</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G11"/>
+  <autoFilter ref="A1:G9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5753,8 +5889,8 @@
   <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="100" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="110" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5777,7 +5913,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Datalink Corporation (Minnesota; Nasdaq: DTLK)</t>
+          <t>Datalink Corporation (Minnesota; IT services and solutions for midsize and large companies)</t>
         </is>
       </c>
     </row>
@@ -5789,7 +5925,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Insight Enterprises, Inc., through its wholly owned subsidiary Reef Acquisition Co.</t>
+          <t>Insight Enterprises, Inc. (Delaware), through its wholly owned subsidiary Reef Acquisition Co.</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5937,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Strategic: Fortune 500 global provider of IT hardware, software, cloud and services (p.19)</t>
+          <t>Strategic: Fortune 500-ranked global provider of IT hardware, software, cloud and service solutions (p. 1)</t>
         </is>
       </c>
     </row>
@@ -5813,7 +5949,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>$11.25 per share in cash, without interest; funded from Insight cash and existing credit facilities; no financing condition (p.48)</t>
+          <t>$11.25 per share in cash, without interest (p. 2). Funded from Insight cash and existing credit facilities; no financing condition (p. 48).</t>
         </is>
       </c>
     </row>
@@ -5825,7 +5961,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>11/06/2016</t>
+          <t>11/06/2016 (evening of Sunday, November 6, 2016)</t>
         </is>
       </c>
     </row>
@@ -5861,7 +5997,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>27–35</t>
+          <t>27-35</t>
         </is>
       </c>
     </row>
@@ -5873,7 +6009,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>mixed: Party A's unsolicited January 2016 proposal began talks; the board then ran a target-led auction from June 2016</t>
+          <t>Bidder-led: Party A's unsolicited January 2016 proposal started the process; the target then ran a broad auction from June 2016.</t>
         </is>
       </c>
     </row>
@@ -5909,7 +6045,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Met (process 1): 23 parties (10 strategic, including Party A, and 13 financial sponsors; p.28, p.36)</t>
+          <t>Met (process 1): 23 parties (10 strategic incl. Party A, Party B and Insight; 13 financial incl. Party C)</t>
         </is>
       </c>
     </row>
@@ -5957,7 +6093,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Faegre Baker Daniels LLP</t>
+          <t>Faegre Baker Daniels LLP (FaegreBD)</t>
         </is>
       </c>
     </row>
@@ -5969,7 +6105,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>In January 2016 strategic Party A made an unsolicited $10.00 cash offer; the board negotiated with it bilaterally but in April rejected its financing-contingent $10.30–$10.75 proposal. In June Raymond James contacted 27 potential buyers, 23 of whom signed NDAs, and ten IOIs were considered; the five highest advanced. Insight, Party B and Party C submitted final proposals with mark-ups; after improvements Insight reached $12.00 and won exclusivity on 09/02. Insight's pro forma accounting demands led the board to let exclusivity lapse and re-approach Party B and Party C; B later withdrew after seeing Q3 results, and C, at $11.25, was denied the Q3 data. After renewed exclusivity Insight cut its price to $11.00 on the Q3 results, then agreed to $11.25, and the merger agreement was signed on 11/06/2016.</t>
+          <t>Datalink's sale began with Party A's unsolicited $10.00 cash proposal in January 2016. The board hired Raymond James and gave Party A an NDA; in April it declined Party A's financing-contingent $10.30-$10.75 proposal. From June 2016 Raymond James approached 27 buyers, 23 of which signed NDAs; nine sent initial indications and the board also counted Party A's standing proposal. The board advanced the five highest bidders and asked for final proposals with merger-agreement mark-ups by 08/30: Party B bid $12.00, Party C $11.00 then $11.25, Insight $11.75 then $12.00, and two did not bid. Insight got exclusivity on 09/02, but its pre-closing 8-K demands led the board to let exclusivity lapse and re-approach Parties B and C; Party B withdrew after seeing third-quarter results, and Party C, at $11.25, was denied the new financials. Insight regained exclusivity on 10/26 and cut its price to $11.00 on 11/01, then agreed to $11.25 on 11/02; the merger agreement was signed on 11/06/2016 and announced on 11/07/2016.</t>
         </is>
       </c>
     </row>
